--- a/reports/devops-jobs-israel-2026-W34.xlsx
+++ b/reports/devops-jobs-israel-2026-W34.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="450">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17T07:10:17</t>
+    <t xml:space="preserve">2026-08-18T06:57:21</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -426,6 +426,15 @@
     <t xml:space="preserve">2026-06-07</t>
   </si>
   <si>
+    <t xml:space="preserve">QA Automation Engineer (Temporary Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8542303002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior Devops Engineer</t>
   </si>
   <si>
@@ -456,783 +465,834 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
   </si>
   <si>
-    <t xml:space="preserve">Devops</t>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Elbit Systems Israel</t>
   </si>
   <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4412813583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (37333)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37333-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4455273849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4451777264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allpha Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allpha-innovation-4454255466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simplex 3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-simplex-3d-4452264625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODDITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-oddity-4452384011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - KubeOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kubeops-team-at-wix-4453083488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4454269739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4454251693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tonkean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-tonkean-4452977126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karmiel, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4450472357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Team lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-compie-technologies-4455300779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead (37248)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-37248-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4455284132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagry | Autonomous Driving</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-imagry-autonomous-driving-4452259211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-descope-4431665949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chamelio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-chamelio-4455249973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer, NCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-4453261687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Data Infrastructure Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-team-leader-at-evoke-4443982712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antidote Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4452991835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-fetcherr-4450173695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-skai-4427485314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualcomm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (GCP | Kubernetes) – Mid Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yarden Abramovich HR Consulting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-gcp-kubernetes-%E2%80%93-mid-level-at-yarden-abramovich-hr-consulting-4451555123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proteanTecs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-proteantecs-4455185136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or HaNer, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4452238627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441563717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4454032601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARMAN International</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-infrastructure-engineer-at-comblack-4455291083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Streaming Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-streaming-platform-engineer-at-nuvei-4455192546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-ai-4450816877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-team-lead-at-zenity-4455197109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend &amp; Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-data-platform-engineer-at-loora-2147625360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Lead - DevOps And Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-lead-devops-and-cloud-at-terasky-4452249308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Staff DevOps Engineer - Cloud Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-cloud-security-at-palo-alto-networks-4450813194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yavne, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-architect-at-sqlink-group-4450469560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-infrastructure-engineer-at-shavit-software-4455295099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4455193277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remedio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-remedio-4427566011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identity &amp; Authentication Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/identity-authentication-infrastructure-engineer-at-logica-it-4452547813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">software development student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-development-student-at-radware-4452112960</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4448158765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4455203355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterfall Security Solutions</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4449808042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4412813583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codevalue-4451527258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (Agentic Search)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-agentic-search-at-nebius-4449552344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODDITY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-oddity-4452384011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - KubeOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kubeops-team-at-wix-4453083488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lod, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4449550588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tonkean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-tonkean-4452977126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4449812270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4449562024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLVTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-tlvtech-4449569052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chamelio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-chamelio-4449841507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eitan Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-eitan-medical-4451528239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coralogix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-coralogix-4442570483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antidote Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4452991835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-fetcherr-4450173695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualcomm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (GCP | Kubernetes) – Mid Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yarden Abramovich HR Consulting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-gcp-kubernetes-%E2%80%93-mid-level-at-yarden-abramovich-hr-consulting-4451555123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solutions / Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APERIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/solutions-site-reliability-engineer-at-aperio-4451514889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer, NCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-ai-4450816877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-comblack-4451546691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4451633831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441563717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4451777264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-4453261687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4454032601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manager, Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crusoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Streaming Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-streaming-platform-engineer-at-nuvei-4455192546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-production-engineering-at-confidential-4452985368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-team-lead-at-zenity-4455197109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eleos Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-eleos-health-4455251513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend &amp; Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-data-platform-engineer-at-loora-2147625360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Client Oriented</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPMG Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-client-oriented-at-kpmg-israel-4451134408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yavne, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-architect-at-sqlink-group-4450469560</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-at-logica-it-4452227142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Environment Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">etoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Engineer I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
   </si>
   <si>
     <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4450457986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-comblack-4454021597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4455193277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remedio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-remedio-4427566011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4448158765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4452408106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterfall Security Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Environment Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MER Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-mer-group-4436525380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
-  </si>
-  <si>
     <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
   </si>
   <si>
@@ -1245,55 +1305,16 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4451682760</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator for Computing Qual (testing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-for-computing-qual-testing-at-applied-materials-israel-4449806027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist – MENTEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PointFive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-security-specialist-at-pointfive-4426311043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moovit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-moovit-4453119234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, CI/CD</t>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1305,19 +1326,19 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation</t>
+    <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">Git</t>
@@ -1472,7 +1493,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7">
@@ -1480,7 +1501,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -1488,7 +1509,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
@@ -1496,7 +1517,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1123</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="10">
@@ -1568,7 +1589,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20">
@@ -1576,7 +1597,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1595,36 +1616,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="B2" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1643,130 +1664,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="B2" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>338</v>
+        <v>434</v>
       </c>
       <c r="B3" s="3">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="B4" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>427</v>
+        <v>341</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="B6" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="B8" s="3">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B9" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>431</v>
+        <v>336</v>
       </c>
       <c r="B10" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>329</v>
+        <v>439</v>
       </c>
       <c r="B13" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1791,13 +1812,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
     </row>
     <row r="2">
@@ -1805,13 +1826,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3">
-        <v>14.0</v>
+        <v>14.6</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1820,88 +1841,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3" s="3">
-        <v>34.9</v>
+        <v>34.6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>7.6</v>
+        <v>8.9</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>31.3</v>
+        <v>28.7</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>18.2</v>
+        <v>17.3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>14.7</v>
+        <v>15.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1913,8 +1934,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="33" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -1985,7 +2006,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -2017,7 +2038,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -2049,7 +2070,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="3">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5">
@@ -2081,7 +2102,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -2113,7 +2134,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -2145,7 +2166,7 @@
         <v>41</v>
       </c>
       <c r="J7" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -2177,7 +2198,7 @@
         <v>67</v>
       </c>
       <c r="J8" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9">
@@ -2209,7 +2230,7 @@
         <v>71</v>
       </c>
       <c r="J9" s="3">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
@@ -2241,7 +2262,7 @@
         <v>67</v>
       </c>
       <c r="J10" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11">
@@ -2273,7 +2294,7 @@
         <v>80</v>
       </c>
       <c r="J11" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
@@ -2305,7 +2326,7 @@
         <v>85</v>
       </c>
       <c r="J12" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -2337,7 +2358,7 @@
         <v>46</v>
       </c>
       <c r="J13" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -2369,7 +2390,7 @@
         <v>92</v>
       </c>
       <c r="J14" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -2401,7 +2422,7 @@
         <v>71</v>
       </c>
       <c r="J15" s="3">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -2433,7 +2454,7 @@
         <v>99</v>
       </c>
       <c r="J16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2465,7 +2486,7 @@
         <v>105</v>
       </c>
       <c r="J17" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18">
@@ -2497,7 +2518,7 @@
         <v>109</v>
       </c>
       <c r="J18" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2529,7 +2550,7 @@
         <v>41</v>
       </c>
       <c r="J19" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2561,7 +2582,7 @@
         <v>119</v>
       </c>
       <c r="J20" s="3">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21">
@@ -2593,7 +2614,7 @@
         <v>124</v>
       </c>
       <c r="J21" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -2625,7 +2646,7 @@
         <v>128</v>
       </c>
       <c r="J22" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -2657,7 +2678,7 @@
         <v>134</v>
       </c>
       <c r="J23" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
@@ -2674,52 +2695,52 @@
         <v>49</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>136</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J24" s="3">
-        <v>6</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>140</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -2727,13 +2748,13 @@
         <v>110</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="D26" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>43</v>
@@ -2743,27 +2764,27 @@
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="J26" s="3">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="D27" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>43</v>
@@ -2773,27 +2794,27 @@
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="J27" s="3">
-        <v>70</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>43</v>
@@ -2803,27 +2824,27 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>41</v>
+        <v>150</v>
       </c>
       <c r="J28" s="3">
-        <v>6</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="D29" s="3" t="s">
-        <v>156</v>
+        <v>49</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>43</v>
@@ -2833,27 +2854,27 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="J29" s="3">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>43</v>
@@ -2863,24 +2884,24 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>41</v>
+        <v>159</v>
       </c>
       <c r="J30" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>116</v>
@@ -2893,27 +2914,27 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>41</v>
+        <v>159</v>
       </c>
       <c r="J31" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>43</v>
@@ -2923,56 +2944,54 @@
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>141</v>
+        <v>99</v>
       </c>
       <c r="J32" s="3">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>49</v>
+        <v>157</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>170</v>
-      </c>
+      <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="J33" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>173</v>
+        <v>110</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>49</v>
@@ -2985,87 +3004,89 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="J34" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>41</v>
+        <v>144</v>
       </c>
       <c r="J35" s="3">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F36" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>175</v>
+      </c>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="J36" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>110</v>
+        <v>178</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>43</v>
@@ -3075,73 +3096,73 @@
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="J37" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>53</v>
+        <v>181</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>49</v>
+        <v>157</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="J38" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>188</v>
+        <v>110</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>191</v>
+        <v>49</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="J39" s="3">
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40">
@@ -3149,10 +3170,10 @@
         <v>53</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>49</v>
@@ -3165,84 +3186,84 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>41</v>
+        <v>188</v>
       </c>
       <c r="J40" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>41</v>
+        <v>159</v>
       </c>
       <c r="J41" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>190</v>
+        <v>142</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>191</v>
+        <v>37</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>41</v>
+        <v>159</v>
       </c>
       <c r="J42" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>49</v>
@@ -3255,27 +3276,27 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>109</v>
+        <v>197</v>
       </c>
       <c r="J43" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>191</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>38</v>
@@ -3288,24 +3309,24 @@
         <v>202</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="J44" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="D45" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>43</v>
@@ -3315,24 +3336,24 @@
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>207</v>
+        <v>159</v>
       </c>
       <c r="J45" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>208</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>49</v>
@@ -3345,27 +3366,27 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="J46" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>38</v>
@@ -3375,27 +3396,27 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>41</v>
+        <v>159</v>
       </c>
       <c r="J47" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>143</v>
+        <v>213</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>49</v>
+        <v>157</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>43</v>
@@ -3405,27 +3426,27 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>217</v>
+        <v>159</v>
       </c>
       <c r="J48" s="3">
-        <v>89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>218</v>
+        <v>53</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>191</v>
+        <v>49</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>38</v>
@@ -3435,86 +3456,84 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>172</v>
+        <v>217</v>
       </c>
       <c r="J49" s="3">
-        <v>4</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>221</v>
+        <v>138</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>223</v>
+        <v>146</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>225</v>
+        <v>159</v>
       </c>
       <c r="J50" s="3">
-        <v>67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>228</v>
+        <v>142</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>229</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>41</v>
+        <v>197</v>
       </c>
       <c r="J51" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>49</v>
@@ -3527,24 +3546,24 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>41</v>
+        <v>159</v>
       </c>
       <c r="J52" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>143</v>
+        <v>208</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>49</v>
@@ -3557,57 +3576,57 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="J53" s="3">
-        <v>67</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>193</v>
+        <v>230</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>187</v>
+        <v>232</v>
       </c>
       <c r="J54" s="3">
-        <v>3</v>
+        <v>90</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>241</v>
+        <v>200</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>116</v>
+        <v>201</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>38</v>
@@ -3617,24 +3636,24 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="J55" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>188</v>
+        <v>236</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>49</v>
@@ -3647,27 +3666,27 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>245</v>
+        <v>105</v>
       </c>
       <c r="J56" s="3">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>249</v>
+        <v>116</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>43</v>
@@ -3677,87 +3696,89 @@
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>99</v>
+        <v>243</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F58" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>246</v>
+      </c>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>254</v>
+        <v>41</v>
       </c>
       <c r="J58" s="3">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>176</v>
+        <v>249</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>257</v>
+        <v>159</v>
       </c>
       <c r="J59" s="3">
-        <v>88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>258</v>
+        <v>53</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>143</v>
+        <v>252</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>49</v>
+        <v>253</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>38</v>
@@ -3767,24 +3788,24 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>261</v>
+        <v>99</v>
       </c>
       <c r="J60" s="3">
-        <v>85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>72</v>
+        <v>255</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>262</v>
+        <v>221</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>143</v>
+        <v>190</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>49</v>
@@ -3797,27 +3818,27 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="J61" s="3">
-        <v>63</v>
+        <v>89</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>248</v>
+        <v>146</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>249</v>
+        <v>49</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>38</v>
@@ -3827,117 +3848,117 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>268</v>
+        <v>153</v>
       </c>
       <c r="J62" s="3">
-        <v>22</v>
+        <v>86</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>143</v>
+        <v>263</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="J63" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>228</v>
+        <v>146</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>99</v>
+        <v>267</v>
       </c>
       <c r="J64" s="3">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>248</v>
+        <v>146</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>249</v>
+        <v>49</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>187</v>
+        <v>85</v>
       </c>
       <c r="J65" s="3">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>237</v>
+        <v>271</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>176</v>
+        <v>272</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>139</v>
+        <v>252</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>37</v>
+        <v>253</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>38</v>
@@ -3947,87 +3968,87 @@
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>187</v>
+        <v>274</v>
       </c>
       <c r="J66" s="3">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>228</v>
+        <v>146</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>187</v>
+        <v>144</v>
       </c>
       <c r="J67" s="3">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>143</v>
+        <v>252</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>49</v>
+        <v>253</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>268</v>
+        <v>197</v>
       </c>
       <c r="J68" s="3">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>43</v>
@@ -4037,70 +4058,70 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>99</v>
+        <v>197</v>
       </c>
       <c r="J69" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="D70" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="J71" s="3">
         <v>0</v>
@@ -4108,13 +4129,13 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>110</v>
+        <v>289</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>49</v>
@@ -4127,100 +4148,100 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>261</v>
+        <v>99</v>
       </c>
       <c r="J72" s="3">
-        <v>85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>294</v>
-      </c>
       <c r="C73" s="3" t="s">
-        <v>248</v>
+        <v>146</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>249</v>
+        <v>49</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="J73" s="3">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>296</v>
+        <v>220</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>99</v>
+        <v>197</v>
       </c>
       <c r="J74" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>143</v>
+        <v>190</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>302</v>
+        <v>99</v>
       </c>
       <c r="J75" s="3">
         <v>1</v>
@@ -4228,121 +4249,121 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>143</v>
+        <v>252</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>49</v>
+        <v>253</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>170</v>
-      </c>
+      <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>41</v>
+        <v>257</v>
       </c>
       <c r="J76" s="3">
-        <v>6</v>
+        <v>89</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>182</v>
+        <v>304</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>307</v>
+        <v>146</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>172</v>
+        <v>306</v>
       </c>
       <c r="J77" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>310</v>
+        <v>251</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>311</v>
+        <v>252</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>116</v>
+        <v>253</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="J78" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>53</v>
+        <v>309</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>313</v>
+        <v>259</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F79" s="3"/>
+      <c r="F79" s="3" t="s">
+        <v>175</v>
+      </c>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="J79" s="3">
         <v>0</v>
@@ -4350,73 +4371,73 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B80" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C80" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="D80" s="3" t="s">
-        <v>156</v>
+        <v>49</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>158</v>
+        <v>313</v>
       </c>
       <c r="J80" s="3">
-        <v>90</v>
+        <v>46</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>240</v>
+        <v>203</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>228</v>
+        <v>315</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>116</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="J81" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>319</v>
+        <v>198</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>49</v>
@@ -4429,24 +4450,24 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>99</v>
+        <v>319</v>
       </c>
       <c r="J82" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>49</v>
@@ -4459,17 +4480,107 @@
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="I83" s="3" t="s">
+      <c r="C84" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H84" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="J83" s="3">
-        <v>34</v>
+      <c r="I84" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J84" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="J85" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="J86" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J83"/>
+  <autoFilter ref="A1:J86"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4553,6 +4664,9 @@
     <hyperlink ref="H81" r:id="rId80"/>
     <hyperlink ref="H82" r:id="rId81"/>
     <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4560,8 +4674,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="1" max="1" width="51" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -4594,32 +4708,32 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>53</v>
+        <v>154</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>94</v>
+        <v>155</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>49</v>
+        <v>156</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>98</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>246</v>
+        <v>160</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>247</v>
+        <v>161</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>248</v>
+        <v>162</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -4627,7 +4741,7 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>250</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4">
@@ -4635,10 +4749,10 @@
         <v>110</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>271</v>
+        <v>166</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>228</v>
+        <v>167</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -4646,18 +4760,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>272</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>282</v>
+        <v>110</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>283</v>
+        <v>169</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -4665,18 +4779,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>284</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>285</v>
+        <v>181</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>286</v>
+        <v>155</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -4684,18 +4798,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>287</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>288</v>
+        <v>53</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>289</v>
+        <v>189</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -4703,18 +4817,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>290</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>296</v>
+        <v>192</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>297</v>
+        <v>193</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -4722,18 +4836,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>298</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>313</v>
+        <v>203</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>248</v>
+        <v>204</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -4741,18 +4855,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>314</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>319</v>
+        <v>206</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>320</v>
+        <v>207</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>143</v>
+        <v>208</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -4760,11 +4874,220 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>321</v>
       </c>
+      <c r="C20" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>332</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G21"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -4775,6 +5098,17 @@
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
+    <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
+    <hyperlink ref="G16" r:id="rId15"/>
+    <hyperlink ref="G17" r:id="rId16"/>
+    <hyperlink ref="G18" r:id="rId17"/>
+    <hyperlink ref="G19" r:id="rId18"/>
+    <hyperlink ref="G20" r:id="rId19"/>
+    <hyperlink ref="G21" r:id="rId20"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4788,15 +5122,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="B2" s="3">
         <v>17</v>
@@ -4804,7 +5138,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B3" s="3">
         <v>16</v>
@@ -4812,7 +5146,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B4" s="3">
         <v>15</v>
@@ -4820,7 +5154,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B5" s="3">
         <v>15</v>
@@ -4828,7 +5162,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="B6" s="3">
         <v>12</v>
@@ -4836,7 +5170,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B7" s="3">
         <v>12</v>
@@ -4844,7 +5178,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B8" s="3">
         <v>11</v>
@@ -4852,7 +5186,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="B9" s="3">
         <v>11</v>
@@ -4860,7 +5194,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
@@ -4868,7 +5202,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
@@ -4876,7 +5210,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -4884,7 +5218,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
@@ -4892,7 +5226,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -4900,7 +5234,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -4908,7 +5242,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -4921,7 +5255,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4930,7 +5264,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2">
@@ -4959,7 +5293,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -4967,7 +5301,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>176</v>
+        <v>259</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -4975,15 +5309,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>240</v>
+        <v>35</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -4991,7 +5325,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -4999,7 +5333,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5007,7 +5341,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5015,7 +5349,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5023,7 +5357,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5031,7 +5365,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5039,7 +5373,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>259</v>
+        <v>221</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5047,10 +5381,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>59</v>
+        <v>251</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5061,23 +5395,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2">
@@ -5113,10 +5447,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>64</v>
+        <v>130</v>
       </c>
       <c r="C4" s="3">
-        <v>7.2</v>
+        <v>8.8</v>
       </c>
       <c r="D4" s="3">
         <v>3</v>
@@ -5127,13 +5461,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="C5" s="3">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="D5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -5141,10 +5475,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>121</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3">
-        <v>6.0</v>
+        <v>6.2</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -5155,10 +5489,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C7" s="3">
-        <v>5.8</v>
+        <v>6.0</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -5169,10 +5503,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C8" s="3">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -5183,10 +5517,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="C9" s="3">
-        <v>5.0</v>
+        <v>5.3</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -5197,10 +5531,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="C10" s="3">
-        <v>4.2</v>
+        <v>4.0</v>
       </c>
       <c r="D10" s="3">
         <v>3</v>
@@ -5211,13 +5545,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="C11" s="3">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -5225,13 +5559,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C12" s="3">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="D12" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -5239,13 +5573,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>111</v>
+        <v>193</v>
       </c>
       <c r="C13" s="3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -5253,7 +5587,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -5267,7 +5601,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>193</v>
+        <v>155</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5281,7 +5615,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>259</v>
+        <v>221</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5307,10 +5641,10 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
     </row>
     <row r="2">
@@ -5329,10 +5663,10 @@
         <v>43</v>
       </c>
       <c r="B3" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4">
@@ -5340,10 +5674,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -5362,7 +5696,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2">
@@ -5370,7 +5704,7 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
@@ -5378,15 +5712,15 @@
         <v>116</v>
       </c>
       <c r="B3" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -5394,12 +5728,12 @@
         <v>37</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>191</v>
+        <v>157</v>
       </c>
       <c r="B6" s="3">
         <v>4</v>
@@ -5415,18 +5749,10 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>156</v>
+        <v>201</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B9" s="3">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5450,10 +5776,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5465,10 +5791,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5494,13 +5820,13 @@
         <v>77</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
@@ -5517,31 +5843,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>356</v>
+        <v>170</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4">
@@ -5549,31 +5875,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>362</v>
+        <v>269</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>241</v>
+        <v>146</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>352</v>
+        <v>368</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>365</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5">
@@ -5581,31 +5907,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>41</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6">
@@ -5613,31 +5939,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>261</v>
+        <v>379</v>
       </c>
     </row>
     <row r="7">
@@ -5645,31 +5971,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>81</v>
+        <v>380</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>76</v>
+        <v>381</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="F7" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>84</v>
+        <v>383</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8">
@@ -5677,31 +6003,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>375</v>
+        <v>280</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>376</v>
+        <v>148</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="F8" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>365</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9">
@@ -5709,31 +6035,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>277</v>
+        <v>81</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>240</v>
+        <v>76</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>228</v>
+        <v>77</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>352</v>
+        <v>368</v>
       </c>
       <c r="F9" s="3">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>278</v>
+        <v>84</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>187</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
@@ -5741,31 +6067,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>42</v>
+        <v>387</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>35</v>
+        <v>388</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>36</v>
+        <v>389</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="F10" s="3">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>45</v>
+        <v>391</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>46</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11">
@@ -5773,31 +6099,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>381</v>
+        <v>280</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>382</v>
+        <v>281</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="F11" s="3">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>385</v>
+        <v>282</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>141</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -5805,31 +6131,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>309</v>
+        <v>393</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>386</v>
+        <v>331</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>387</v>
+        <v>252</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="F12" s="3">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>390</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -5837,7 +6163,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>391</v>
+        <v>42</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>35</v>
@@ -5846,22 +6172,22 @@
         <v>36</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>352</v>
+        <v>368</v>
       </c>
       <c r="F13" s="3">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>393</v>
+        <v>45</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>141</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
@@ -5869,31 +6195,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>396</v>
+        <v>162</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>352</v>
+        <v>399</v>
       </c>
       <c r="F14" s="3">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>399</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15">
@@ -5901,31 +6227,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>205</v>
+        <v>146</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>352</v>
+        <v>399</v>
       </c>
       <c r="F15" s="3">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>128</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -5933,31 +6259,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>309</v>
+        <v>406</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>404</v>
+        <v>35</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>405</v>
+        <v>36</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="F16" s="3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17">
@@ -5965,31 +6291,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>151</v>
+        <v>410</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="F17" s="3">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>41</v>
+        <v>413</v>
       </c>
     </row>
     <row r="18">
@@ -5997,31 +6323,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>294</v>
+        <v>414</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>143</v>
+        <v>415</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="F18" s="3">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="19">
@@ -6029,31 +6355,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="F19" s="3">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>187</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20">
@@ -6061,31 +6387,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="F20" s="3">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>172</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21">
@@ -6093,31 +6419,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>317</v>
+        <v>423</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>240</v>
+        <v>428</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>228</v>
+        <v>190</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="F21" s="3">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>318</v>
+        <v>430</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>187</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W34.xlsx
+++ b/reports/devops-jobs-israel-2026-W34.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="458">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-18T06:57:21</t>
+    <t xml:space="preserve">2026-08-19T06:58:03</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2%</t>
+    <t xml:space="preserve">1.1%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -444,6 +444,21 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
   </si>
   <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
     <t xml:space="preserve">AllCloud</t>
   </si>
   <si>
@@ -456,13 +471,25 @@
     <t xml:space="preserve">2026-07-22</t>
   </si>
   <si>
-    <t xml:space="preserve">Fiverr</t>
+    <t xml:space="preserve">Agora</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-agora-4451343371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penlink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-penlink-4455777719</t>
   </si>
   <si>
     <t xml:space="preserve">Paragon</t>
@@ -501,6 +528,12 @@
     <t xml:space="preserve">2026-08-18</t>
   </si>
   <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4452584141</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Engineer (37333)</t>
   </si>
   <si>
@@ -513,12 +546,492 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37333-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4455273849</t>
   </si>
   <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gini-apps-4455709981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Principal, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-descope-4431665949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chamelio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-chamelio-4455249973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tonkean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-tonkean-4452977126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gotfriends</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4451777264</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4454269739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4454251693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karmiel, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4450472357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Team lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-compie-technologies-4455300779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead (37248)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-37248-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4455284132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earnix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4452892941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagry | Autonomous Driving</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-imagry-autonomous-driving-4452259211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer, NCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-4453269633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Staff DevOps Engineer - Cloud Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-cloud-security-at-palo-alto-networks-4450813194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-skai-4427485314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441571472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - KubeOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kubeops-team-at-wix-4453083488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4454032601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antidote Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4452991835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-infrastructure-engineer-at-comblack-4455291083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Streaming Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-streaming-platform-engineer-at-nuvei-4455192546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Data Infrastructure Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-team-leader-at-evoke-4443982712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appcharge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-appcharge-4454760249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-ai-4450816877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-team-lead-at-zenity-4455197109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simplex 3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-simplex-3d-4452264625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-fetcherr-4450173695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4455938126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODDITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-oddity-4452384011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend &amp; Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-data-platform-engineer-at-loora-2147625360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Lead - DevOps And Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-lead-devops-and-cloud-at-terasky-4452249308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Lead Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-infrastructure-engineer-at-sela-4454743727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yavne, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-architect-at-sqlink-group-4450469560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4455193277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-at-abra-4454749355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or HaNer, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4452238627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-infrastructure-engineer-at-shavit-software-4455295099</t>
+  </si>
+  <si>
     <t xml:space="preserve">Allpha Innovation</t>
   </si>
   <si>
@@ -528,681 +1041,192 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allpha-innovation-4454255466</t>
   </si>
   <si>
-    <t xml:space="preserve">Simplex 3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-simplex-3d-4452264625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODDITY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-oddity-4452384011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - KubeOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kubeops-team-at-wix-4453083488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4454269739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4454251693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tonkean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-tonkean-4452977126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Karmiel, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4450472357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Team lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-compie-technologies-4455300779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead (37248)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-37248-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4455284132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imagry | Autonomous Driving</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-imagry-autonomous-driving-4452259211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-descope-4431665949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chamelio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-chamelio-4455249973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer, NCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-4453261687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Data Infrastructure Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-team-leader-at-evoke-4443982712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antidote Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4452991835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-fetcherr-4450173695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-skai-4427485314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualcomm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (GCP | Kubernetes) – Mid Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yarden Abramovich HR Consulting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-gcp-kubernetes-%E2%80%93-mid-level-at-yarden-abramovich-hr-consulting-4451555123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proteanTecs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-proteantecs-4455185136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or HaNer, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4452238627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441563717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4454032601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARMAN International</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-infrastructure-engineer-at-comblack-4455291083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Streaming Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-streaming-platform-engineer-at-nuvei-4455192546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-ai-4450816877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-team-lead-at-zenity-4455197109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend &amp; Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-data-platform-engineer-at-loora-2147625360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Lead - DevOps And Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-lead-devops-and-cloud-at-terasky-4452249308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Staff DevOps Engineer - Cloud Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-cloud-security-at-palo-alto-networks-4450813194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yavne, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-architect-at-sqlink-group-4450469560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-infrastructure-engineer-at-shavit-software-4455295099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4455193277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remedio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-remedio-4427566011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identity &amp; Authentication Infrastructure Engineer</t>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Full Stack Developer - Data Loss Prevention Cloud Service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-full-stack-developer-data-loss-prevention-cloud-service-at-check-point-software-4455339838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4448158765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4455203355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterfall Security Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Logica-IT</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/identity-authentication-infrastructure-engineer-at-logica-it-4452547813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">software development student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-development-student-at-radware-4452112960</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4448158765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4455203355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterfall Security Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation</t>
   </si>
   <si>
@@ -1212,63 +1236,63 @@
     <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">Test Environment Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Cloud (any), Kubernetes, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4452294600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">etoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
   </si>
   <si>
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">etoro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -1278,27 +1302,12 @@
     <t xml:space="preserve">2026-07-01</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Operations Engineer I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
     <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
   </si>
   <si>
@@ -1317,6 +1326,24 @@
     <t xml:space="preserve">2026-07-31</t>
   </si>
   <si>
+    <t xml:space="preserve">System Administrator for Computing Qual (testing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-for-computing-qual-testing-at-applied-materials-israel-4449806027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
@@ -1332,16 +1359,13 @@
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1493,7 +1517,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7">
@@ -1501,7 +1525,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -1509,7 +1533,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -1517,7 +1541,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1126</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="10">
@@ -1589,7 +1613,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20">
@@ -1597,7 +1621,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1616,38 +1640,46 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="B2" s="3">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B5" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="B6" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1664,23 +1696,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="B2" s="3">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>434</v>
+        <v>351</v>
       </c>
       <c r="B3" s="3">
         <v>31</v>
@@ -1688,47 +1720,47 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B4" s="3">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>341</v>
+        <v>443</v>
       </c>
       <c r="B5" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B6" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="B7" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>437</v>
+        <v>346</v>
       </c>
       <c r="B8" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>339</v>
+        <v>446</v>
       </c>
       <c r="B9" s="3">
         <v>18</v>
@@ -1736,39 +1768,39 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>336</v>
+        <v>447</v>
       </c>
       <c r="B10" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>438</v>
+        <v>343</v>
       </c>
       <c r="B11" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="B12" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>439</v>
+        <v>342</v>
       </c>
       <c r="B13" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B14" s="3">
         <v>11</v>
@@ -1776,18 +1808,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>338</v>
+        <v>448</v>
       </c>
       <c r="B15" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>440</v>
+        <v>344</v>
       </c>
       <c r="B16" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1812,13 +1844,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
     </row>
     <row r="2">
@@ -1826,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3">
-        <v>14.6</v>
+        <v>28.5</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1841,88 +1873,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C3" s="3">
-        <v>34.6</v>
+        <v>36.7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>28.7</v>
+        <v>33.8</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>17.3</v>
+        <v>20.7</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>15.0</v>
+        <v>16.4</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2006,7 +2038,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -2038,7 +2070,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -2070,7 +2102,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5">
@@ -2102,7 +2134,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -2134,7 +2166,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -2166,7 +2198,7 @@
         <v>41</v>
       </c>
       <c r="J7" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -2198,7 +2230,7 @@
         <v>67</v>
       </c>
       <c r="J8" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9">
@@ -2230,7 +2262,7 @@
         <v>71</v>
       </c>
       <c r="J9" s="3">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -2262,7 +2294,7 @@
         <v>67</v>
       </c>
       <c r="J10" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -2294,7 +2326,7 @@
         <v>80</v>
       </c>
       <c r="J11" s="3">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12">
@@ -2326,7 +2358,7 @@
         <v>85</v>
       </c>
       <c r="J12" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -2358,7 +2390,7 @@
         <v>46</v>
       </c>
       <c r="J13" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -2390,7 +2422,7 @@
         <v>92</v>
       </c>
       <c r="J14" s="3">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15">
@@ -2422,7 +2454,7 @@
         <v>71</v>
       </c>
       <c r="J15" s="3">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -2454,7 +2486,7 @@
         <v>99</v>
       </c>
       <c r="J16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -2486,7 +2518,7 @@
         <v>105</v>
       </c>
       <c r="J17" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18">
@@ -2518,7 +2550,7 @@
         <v>109</v>
       </c>
       <c r="J18" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -2550,7 +2582,7 @@
         <v>41</v>
       </c>
       <c r="J19" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -2582,7 +2614,7 @@
         <v>119</v>
       </c>
       <c r="J20" s="3">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21">
@@ -2614,7 +2646,7 @@
         <v>124</v>
       </c>
       <c r="J21" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -2646,7 +2678,7 @@
         <v>128</v>
       </c>
       <c r="J22" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -2678,7 +2710,7 @@
         <v>134</v>
       </c>
       <c r="J23" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24">
@@ -2708,7 +2740,7 @@
         <v>137</v>
       </c>
       <c r="J24" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25">
@@ -2740,37 +2772,39 @@
         <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F26" s="3"/>
+      <c r="F26" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="G26" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J26" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2778,13 +2812,13 @@
         <v>110</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>43</v>
@@ -2794,13 +2828,13 @@
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="J27" s="3">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28">
@@ -2808,10 +2842,10 @@
         <v>110</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>49</v>
@@ -2824,13 +2858,13 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J28" s="3">
-        <v>85</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
@@ -2838,10 +2872,10 @@
         <v>110</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>49</v>
@@ -2854,27 +2888,27 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="J29" s="3">
-        <v>86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>157</v>
+        <v>49</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>43</v>
@@ -2890,21 +2924,21 @@
         <v>159</v>
       </c>
       <c r="J30" s="3">
-        <v>0</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="C31" s="3" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>43</v>
@@ -2914,27 +2948,27 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J31" s="3">
-        <v>0</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>110</v>
+        <v>163</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>164</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>43</v>
@@ -2944,10 +2978,10 @@
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="J32" s="3">
         <v>1</v>
@@ -2958,13 +2992,13 @@
         <v>110</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>157</v>
+        <v>49</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>43</v>
@@ -2974,10 +3008,10 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="J33" s="3">
         <v>0</v>
@@ -2985,16 +3019,16 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>110</v>
+        <v>171</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>43</v>
@@ -3004,24 +3038,24 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="J34" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>49</v>
@@ -3034,89 +3068,87 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J35" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>47</v>
+        <v>138</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>175</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J36" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="J37" s="3">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>181</v>
+        <v>110</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>157</v>
+        <v>49</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>43</v>
@@ -3126,43 +3158,43 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="J38" s="3">
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="J39" s="3">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -3170,10 +3202,10 @@
         <v>53</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>49</v>
@@ -3186,117 +3218,117 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="J40" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="J41" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>197</v>
+        <v>99</v>
       </c>
       <c r="J43" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>38</v>
@@ -3306,147 +3338,147 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="J44" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>208</v>
+        <v>147</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>210</v>
+        <v>110</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>161</v>
+        <v>213</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>162</v>
+        <v>214</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>116</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>110</v>
+        <v>216</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>157</v>
+        <v>49</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>53</v>
+        <v>220</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>215</v>
+        <v>172</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>38</v>
@@ -3456,24 +3488,24 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>217</v>
+        <v>168</v>
       </c>
       <c r="J49" s="3">
-        <v>55</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>138</v>
+        <v>53</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>218</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>49</v>
@@ -3486,57 +3518,57 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>159</v>
+        <v>224</v>
       </c>
       <c r="J50" s="3">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>197</v>
+        <v>145</v>
       </c>
       <c r="J51" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>223</v>
+        <v>110</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>170</v>
+        <v>229</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>49</v>
+        <v>166</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>43</v>
@@ -3546,24 +3578,24 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>208</v>
+        <v>151</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>49</v>
@@ -3576,84 +3608,86 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>197</v>
+        <v>234</v>
       </c>
       <c r="J53" s="3">
-        <v>4</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>232</v>
+        <v>145</v>
       </c>
       <c r="J54" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>201</v>
+        <v>241</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F55" s="3"/>
+      <c r="F55" s="3" t="s">
+        <v>242</v>
+      </c>
       <c r="G55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="J55" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>49</v>
@@ -3666,27 +3700,27 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>105</v>
       </c>
       <c r="J56" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>240</v>
+        <v>164</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>241</v>
+        <v>165</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>43</v>
@@ -3696,89 +3730,87 @@
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>243</v>
+        <v>168</v>
       </c>
       <c r="J57" s="3">
-        <v>68</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>246</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>41</v>
+        <v>251</v>
       </c>
       <c r="J58" s="3">
-        <v>7</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>252</v>
+        <v>151</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>253</v>
+        <v>49</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>38</v>
@@ -3788,57 +3820,57 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>99</v>
+        <v>256</v>
       </c>
       <c r="J60" s="3">
-        <v>1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>255</v>
+        <v>141</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>221</v>
+        <v>257</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>190</v>
+        <v>151</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>257</v>
+        <v>85</v>
       </c>
       <c r="J61" s="3">
-        <v>89</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>146</v>
+        <v>240</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>49</v>
+        <v>241</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>38</v>
@@ -3848,27 +3880,27 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>153</v>
+        <v>262</v>
       </c>
       <c r="J62" s="3">
-        <v>86</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>263</v>
+        <v>151</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>43</v>
@@ -3878,27 +3910,27 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="J63" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>72</v>
+        <v>266</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>146</v>
+        <v>240</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>49</v>
+        <v>241</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>38</v>
@@ -3908,24 +3940,24 @@
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>267</v>
+        <v>193</v>
       </c>
       <c r="J64" s="3">
-        <v>64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>49</v>
@@ -3938,54 +3970,54 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>85</v>
+        <v>145</v>
       </c>
       <c r="J65" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>252</v>
+        <v>173</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>253</v>
+        <v>116</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>274</v>
+        <v>193</v>
       </c>
       <c r="J66" s="3">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>259</v>
-      </c>
       <c r="C67" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>49</v>
@@ -4001,24 +4033,24 @@
         <v>276</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>144</v>
+        <v>277</v>
       </c>
       <c r="J67" s="3">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>252</v>
+        <v>218</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>253</v>
+        <v>49</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>38</v>
@@ -4028,24 +4060,24 @@
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="J68" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>116</v>
@@ -4061,10 +4093,10 @@
         <v>282</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="J69" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4075,40 +4107,40 @@
         <v>284</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>285</v>
+        <v>151</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="J70" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>281</v>
-      </c>
       <c r="C71" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>43</v>
@@ -4121,21 +4153,21 @@
         <v>288</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="J71" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>290</v>
-      </c>
       <c r="C72" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>49</v>
@@ -4148,24 +4180,24 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="J72" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>292</v>
+        <v>235</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>49</v>
@@ -4178,24 +4210,24 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>243</v>
+        <v>193</v>
       </c>
       <c r="J73" s="3">
-        <v>68</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>220</v>
+        <v>293</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>146</v>
+        <v>186</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>49</v>
@@ -4208,40 +4240,40 @@
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>197</v>
+        <v>99</v>
       </c>
       <c r="J74" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>297</v>
+        <v>110</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="J75" s="3">
         <v>1</v>
@@ -4249,46 +4281,46 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>252</v>
+        <v>205</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>253</v>
+        <v>206</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>257</v>
+        <v>208</v>
       </c>
       <c r="J76" s="3">
-        <v>89</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>146</v>
+        <v>240</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>49</v>
+        <v>241</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>43</v>
@@ -4298,40 +4330,40 @@
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>306</v>
+        <v>251</v>
       </c>
       <c r="J77" s="3">
-        <v>2</v>
+        <v>90</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>251</v>
+        <v>305</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>253</v>
+        <v>166</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="J78" s="3">
         <v>0</v>
@@ -4339,78 +4371,78 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>309</v>
+        <v>47</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>259</v>
+        <v>307</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>252</v>
+        <v>151</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>253</v>
+        <v>49</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>175</v>
+        <v>242</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="J79" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>193</v>
+        <v>310</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>313</v>
+        <v>179</v>
       </c>
       <c r="J80" s="3">
-        <v>46</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>203</v>
+        <v>313</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>315</v>
+        <v>240</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>116</v>
+        <v>241</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>38</v>
@@ -4420,27 +4452,27 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="J81" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>198</v>
+        <v>315</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>38</v>
@@ -4450,54 +4482,54 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>319</v>
+        <v>145</v>
       </c>
       <c r="J82" s="3">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>321</v>
+        <v>213</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>190</v>
+        <v>319</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>323</v>
+        <v>203</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>49</v>
@@ -4510,77 +4542,167 @@
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>99</v>
+        <v>323</v>
       </c>
       <c r="J84" s="3">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>190</v>
+        <v>151</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>329</v>
+        <v>99</v>
       </c>
       <c r="J85" s="3">
-        <v>35</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="J86" s="3">
         <v>0</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J87" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J88" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J89" s="3">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J86"/>
+  <autoFilter ref="A1:J89"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4667,6 +4789,9 @@
     <hyperlink ref="H84" r:id="rId83"/>
     <hyperlink ref="H85" r:id="rId84"/>
     <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4674,8 +4799,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="51" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -4708,32 +4833,32 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>156</v>
+        <v>49</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -4741,7 +4866,7 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4">
@@ -4749,10 +4874,10 @@
         <v>110</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -4760,7 +4885,7 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5">
@@ -4768,10 +4893,10 @@
         <v>110</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -4779,18 +4904,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>181</v>
+        <v>110</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>155</v>
+        <v>225</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>156</v>
+        <v>226</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -4798,18 +4923,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>182</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>53</v>
+        <v>235</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>189</v>
+        <v>236</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>190</v>
+        <v>151</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -4817,18 +4942,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>191</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>192</v>
+        <v>269</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>193</v>
+        <v>270</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -4836,7 +4961,7 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>194</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9">
@@ -4844,10 +4969,10 @@
         <v>110</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>203</v>
+        <v>289</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>204</v>
+        <v>151</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -4855,18 +4980,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>205</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>206</v>
+        <v>304</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>207</v>
+        <v>305</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -4874,18 +4999,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>209</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>210</v>
+        <v>315</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>161</v>
+        <v>316</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -4893,18 +5018,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>211</v>
+        <v>317</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>110</v>
+        <v>327</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>212</v>
+        <v>328</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>213</v>
+        <v>173</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -4912,182 +5037,11 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G21"/>
+  <autoFilter ref="A1:G12"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5100,15 +5054,6 @@
     <hyperlink ref="G10" r:id="rId9"/>
     <hyperlink ref="G11" r:id="rId10"/>
     <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
-    <hyperlink ref="G20" r:id="rId19"/>
-    <hyperlink ref="G21" r:id="rId20"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5122,15 +5067,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B2" s="3">
         <v>17</v>
@@ -5138,7 +5083,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B3" s="3">
         <v>16</v>
@@ -5146,7 +5091,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>337</v>
+        <v>242</v>
       </c>
       <c r="B4" s="3">
         <v>15</v>
@@ -5154,15 +5099,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>175</v>
+        <v>344</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="B6" s="3">
         <v>12</v>
@@ -5170,7 +5115,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="B7" s="3">
         <v>12</v>
@@ -5178,7 +5123,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="B8" s="3">
         <v>11</v>
@@ -5186,7 +5131,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="B9" s="3">
         <v>11</v>
@@ -5194,7 +5139,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>342</v>
+        <v>143</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
@@ -5202,7 +5147,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
@@ -5210,7 +5155,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -5218,7 +5163,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
@@ -5226,7 +5171,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -5234,7 +5179,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5242,7 +5187,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5264,7 +5209,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2">
@@ -5301,15 +5246,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>259</v>
+        <v>35</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5317,7 +5262,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5325,7 +5270,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5333,7 +5278,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>121</v>
+        <v>164</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5341,7 +5286,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5349,7 +5294,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5357,7 +5302,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5365,7 +5310,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>203</v>
+        <v>236</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5373,7 +5318,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5381,7 +5326,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5402,16 +5347,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2">
@@ -5531,13 +5476,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>259</v>
+        <v>111</v>
       </c>
       <c r="C10" s="3">
-        <v>4.0</v>
+        <v>2.9</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -5545,13 +5490,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>111</v>
+        <v>172</v>
       </c>
       <c r="C11" s="3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5559,7 +5504,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="C12" s="3">
         <v>2.8</v>
@@ -5573,7 +5518,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -5587,10 +5532,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>203</v>
+        <v>239</v>
       </c>
       <c r="C14" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D14" s="3">
         <v>2</v>
@@ -5601,7 +5546,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5615,7 +5560,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5641,10 +5586,10 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
     </row>
     <row r="2">
@@ -5663,10 +5608,10 @@
         <v>43</v>
       </c>
       <c r="B3" s="3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4">
@@ -5674,10 +5619,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>
@@ -5696,7 +5641,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2">
@@ -5704,7 +5649,7 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
@@ -5712,20 +5657,20 @@
         <v>116</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>253</v>
+        <v>166</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>37</v>
+        <v>241</v>
       </c>
       <c r="B5" s="3">
         <v>5</v>
@@ -5733,7 +5678,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>157</v>
+        <v>37</v>
       </c>
       <c r="B6" s="3">
         <v>4</v>
@@ -5749,7 +5694,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5776,10 +5721,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5791,10 +5736,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5820,13 +5765,13 @@
         <v>77</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
@@ -5843,31 +5788,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4">
@@ -5875,31 +5820,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>269</v>
+        <v>374</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5">
@@ -5907,31 +5852,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6">
@@ -5939,31 +5884,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7">
@@ -5971,28 +5916,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="F7" s="3">
         <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>99</v>
@@ -6003,28 +5948,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="F8" s="3">
         <v>100</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>119</v>
@@ -6044,13 +5989,13 @@
         <v>77</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="F9" s="3">
         <v>92</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>24</v>
@@ -6067,31 +6012,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="F10" s="3">
         <v>92</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11">
@@ -6099,31 +6044,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="F11" s="3">
         <v>88</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -6131,28 +6076,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="F12" s="3">
         <v>88</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>99</v>
@@ -6172,13 +6117,13 @@
         <v>36</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="F13" s="3">
         <v>83</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>24</v>
@@ -6195,31 +6140,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="F14" s="3">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15">
@@ -6227,31 +6172,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>403</v>
+        <v>35</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>146</v>
+        <v>36</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="F15" s="3">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>80</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16">
@@ -6259,31 +6204,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>35</v>
+        <v>257</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>36</v>
+        <v>151</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="F16" s="3">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17">
@@ -6291,31 +6236,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="F17" s="3">
         <v>52</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="18">
@@ -6323,31 +6268,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="F18" s="3">
         <v>51</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
     </row>
     <row r="19">
@@ -6355,31 +6300,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="F19" s="3">
         <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20">
@@ -6387,31 +6332,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>425</v>
+        <v>186</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="F20" s="3">
         <v>48</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>109</v>
+        <v>434</v>
       </c>
     </row>
     <row r="21">
@@ -6419,31 +6364,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>190</v>
+        <v>437</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="F21" s="3">
         <v>48</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>431</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W34.xlsx
+++ b/reports/devops-jobs-israel-2026-W34.xlsx
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19T06:58:03</t>
+    <t xml:space="preserve">2026-08-20T06:58:46</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -225,6 +225,18 @@
     <t xml:space="preserve">2026-06-14</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior DevSecOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4704221006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior Director of Platform Security</t>
   </si>
   <si>
@@ -426,226 +438,610 @@
     <t xml:space="preserve">2026-06-07</t>
   </si>
   <si>
-    <t xml:space="preserve">QA Automation Engineer (Temporary Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8542303002</t>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AllCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4443370175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CommBox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4456470553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-agora-4451343371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4442854342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4452584141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gini-apps-4455709981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-27</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AllCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4443370175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-agora-4451343371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penlink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-penlink-4455777719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4412813583</t>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Principal, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-descope-4431665949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tonkean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-tonkean-4452977126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allpha Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allpha-innovation-4454255466</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-18</t>
   </si>
   <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4452584141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (37333)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earnix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer, NCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-ai-4450816877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cyera-4456176236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devsecops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-dialog-4452580295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-4453261687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Data Infrastructure Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-team-leader-at-evoke-4443982712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antidote Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4452991835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eyesAtop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-eyesatop-4454764581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-skai-4427485314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or HaNer, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4452238627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
   </si>
   <si>
     <t xml:space="preserve">Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37333-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4455273849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gini-apps-4455709981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Principal, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-descope-4431665949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chamelio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-chamelio-4455249973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tonkean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-tonkean-4452977126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4451777264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-infrastructure-engineer-at-comblack-4455291083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appcharge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-appcharge-4454760249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simplex 3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-simplex-3d-4452264625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Streaming Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-streaming-platform-engineer-at-nuvei-4455192546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer – Kubernetes &amp; AI - 4664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bynet Software Systems Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%E2%80%93-kubernetes-ai-4664-at-bynet-software-systems-ltd-4454492747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4455938126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4454032601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend &amp; Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-data-platform-engineer-at-loora-2147625360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4454251693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Lead - DevOps And Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-lead-devops-and-cloud-at-terasky-4452249308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Staff DevOps Engineer - Cloud Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-cloud-security-at-palo-alto-networks-4450813194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Lead Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-infrastructure-engineer-at-sela-4454743727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4455193277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-at-abra-4454749355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-infrastructure-engineer-at-shavit-software-4455295099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identity &amp; Authentication Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/identity-authentication-infrastructure-engineer-at-logica-it-4452547813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-comblack-4454021597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-jobgether-4454997118</t>
   </si>
   <si>
     <t xml:space="preserve">Sunbit</t>
@@ -654,393 +1050,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4454269739</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4454251693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Karmiel, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4450472357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Team lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-compie-technologies-4455300779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead (37248)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-37248-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4455284132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earnix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4452892941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imagry | Autonomous Driving</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-imagry-autonomous-driving-4452259211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer, NCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-4453269633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Staff DevOps Engineer - Cloud Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-cloud-security-at-palo-alto-networks-4450813194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-skai-4427485314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441571472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - KubeOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kubeops-team-at-wix-4453083488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4454032601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antidote Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4452991835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-infrastructure-engineer-at-comblack-4455291083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Streaming Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-streaming-platform-engineer-at-nuvei-4455192546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Data Infrastructure Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-team-leader-at-evoke-4443982712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appcharge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-appcharge-4454760249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-ai-4450816877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-team-lead-at-zenity-4455197109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simplex 3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-simplex-3d-4452264625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-fetcherr-4450173695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4455938126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODDITY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-oddity-4452384011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend &amp; Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-data-platform-engineer-at-loora-2147625360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Lead - DevOps And Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-lead-devops-and-cloud-at-terasky-4452249308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Lead Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-infrastructure-engineer-at-sela-4454743727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yavne, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-architect-at-sqlink-group-4450469560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4455193277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-at-abra-4454749355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or HaNer, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4452238627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-infrastructure-engineer-at-shavit-software-4455295099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allpha Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allpha-innovation-4454255466</t>
-  </si>
-  <si>
     <t xml:space="preserve">Skill</t>
   </si>
   <si>
@@ -1053,9 +1062,6 @@
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
     <t xml:space="preserve">Docker</t>
   </si>
   <si>
@@ -1101,10 +1107,7 @@
     <t xml:space="preserve">Percent</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1%</t>
+    <t xml:space="preserve">49.4%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1164,69 +1167,51 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
   </si>
   <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4448158765</t>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4455765409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterfall Security Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-03</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4455203355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterfall Security Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">Systems Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation</t>
   </si>
   <si>
@@ -1257,15 +1242,6 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Cloud (any), Kubernetes, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4452294600</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Administrator &amp; IT</t>
   </si>
   <si>
@@ -1341,6 +1317,27 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-for-computing-qual-testing-at-applied-materials-israel-4449806027</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Specialist – MENTEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4455175909</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
@@ -1356,16 +1353,19 @@
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1517,7 +1517,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7">
@@ -1533,7 +1533,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
@@ -1541,7 +1541,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1111</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="10">
@@ -1613,7 +1613,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -1640,36 +1640,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="B2" s="3">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1677,7 +1677,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1696,66 +1696,66 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B2" s="3">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B3" s="3">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B4" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B5" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B6" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B7" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>346</v>
+        <v>445</v>
       </c>
       <c r="B8" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -1768,7 +1768,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>447</v>
+        <v>348</v>
       </c>
       <c r="B10" s="3">
         <v>17</v>
@@ -1776,7 +1776,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B11" s="3">
         <v>13</v>
@@ -1784,15 +1784,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>350</v>
+        <v>447</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="B13" s="3">
         <v>12</v>
@@ -1808,18 +1808,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>448</v>
+        <v>347</v>
       </c>
       <c r="B15" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>344</v>
+        <v>448</v>
       </c>
       <c r="B16" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1861,7 +1861,7 @@
         <v>25</v>
       </c>
       <c r="C2" s="3">
-        <v>28.5</v>
+        <v>12.5</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>452</v>
@@ -1873,10 +1873,10 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C3" s="3">
-        <v>36.7</v>
+        <v>34.7</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>452</v>
@@ -1891,7 +1891,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.5</v>
+        <v>9.3</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>452</v>
@@ -1906,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>452</v>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>33.8</v>
+        <v>35.1</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>452</v>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>20.7</v>
+        <v>20.3</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>452</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>452</v>
@@ -1966,7 +1966,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2038,7 +2038,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2070,7 +2070,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -2102,7 +2102,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="3">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5">
@@ -2134,7 +2134,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -2166,7 +2166,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -2198,7 +2198,7 @@
         <v>41</v>
       </c>
       <c r="J7" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -2230,7 +2230,7 @@
         <v>67</v>
       </c>
       <c r="J8" s="3">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9">
@@ -2262,7 +2262,7 @@
         <v>71</v>
       </c>
       <c r="J9" s="3">
-        <v>83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2291,21 +2291,21 @@
         <v>74</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="J10" s="3">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>49</v>
@@ -2314,68 +2314,68 @@
         <v>38</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="J11" s="3">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="D12" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="J12" s="3">
-        <v>22</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>87</v>
@@ -2387,7 +2387,7 @@
         <v>88</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="J13" s="3">
         <v>23</v>
@@ -2395,13 +2395,13 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>49</v>
@@ -2410,19 +2410,19 @@
         <v>38</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="J14" s="3">
-        <v>82</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
@@ -2430,10 +2430,10 @@
         <v>93</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>49</v>
@@ -2442,16 +2442,16 @@
         <v>38</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="J15" s="3">
         <v>83</v>
@@ -2459,13 +2459,13 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>49</v>
@@ -2474,65 +2474,65 @@
         <v>38</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="J16" s="3">
-        <v>2</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J17" s="3">
-        <v>45</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="D18" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>43</v>
@@ -2550,7 +2550,7 @@
         <v>109</v>
       </c>
       <c r="J18" s="3">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19">
@@ -2558,28 +2558,28 @@
         <v>110</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="J19" s="3">
         <v>8</v>
@@ -2587,77 +2587,77 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>47</v>
+        <v>114</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>115</v>
+        <v>49</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="J20" s="3">
-        <v>68</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="E21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="J21" s="3">
-        <v>20</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="C22" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>49</v>
@@ -2678,7 +2678,7 @@
         <v>128</v>
       </c>
       <c r="J22" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -2686,10 +2686,10 @@
         <v>129</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>49</v>
@@ -2698,60 +2698,62 @@
         <v>38</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J23" s="3">
-        <v>73</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="D24" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F24" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>136</v>
+      </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J24" s="3">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>49</v>
@@ -2760,27 +2762,27 @@
         <v>38</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>49</v>
@@ -2792,33 +2794,33 @@
         <v>43</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J26" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>43</v>
@@ -2828,27 +2830,27 @@
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J27" s="3">
-        <v>28</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>43</v>
@@ -2858,24 +2860,24 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J28" s="3">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>49</v>
@@ -2888,10 +2890,10 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>145</v>
+        <v>71</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -2899,13 +2901,13 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>49</v>
@@ -2918,24 +2920,24 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J30" s="3">
-        <v>86</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>49</v>
@@ -2948,10 +2950,10 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J31" s="3">
         <v>87</v>
@@ -2959,16 +2961,16 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>163</v>
+        <v>114</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>164</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>166</v>
+        <v>49</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>43</v>
@@ -2978,27 +2980,27 @@
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J32" s="3">
-        <v>1</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>110</v>
+        <v>167</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="D33" s="3" t="s">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>43</v>
@@ -3008,27 +3010,27 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>145</v>
+        <v>89</v>
       </c>
       <c r="J33" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>171</v>
+        <v>114</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>172</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>43</v>
@@ -3038,10 +3040,10 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="J34" s="3">
         <v>1</v>
@@ -3049,13 +3051,13 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>49</v>
@@ -3068,27 +3070,27 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J35" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>177</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>38</v>
@@ -3098,27 +3100,27 @@
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J36" s="3">
-        <v>3</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>182</v>
+        <v>148</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>38</v>
@@ -3128,18 +3130,18 @@
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="I37" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="J37" s="3">
-        <v>42</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>110</v>
+        <v>184</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>185</v>
@@ -3148,10 +3150,10 @@
         <v>186</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
@@ -3164,51 +3166,51 @@
         <v>188</v>
       </c>
       <c r="J38" s="3">
-        <v>56</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>189</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="J39" s="3">
-        <v>1</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>53</v>
+        <v>193</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>49</v>
+        <v>195</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>38</v>
@@ -3218,117 +3220,117 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="J40" s="3">
-        <v>5</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>155</v>
+        <v>190</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="J41" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>197</v>
+        <v>114</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="J42" s="3">
-        <v>47</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>110</v>
+        <v>203</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>99</v>
+        <v>206</v>
       </c>
       <c r="J43" s="3">
-        <v>2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>38</v>
@@ -3338,57 +3340,57 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="J44" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>168</v>
+        <v>214</v>
       </c>
       <c r="J45" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>43</v>
@@ -3398,10 +3400,10 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="J46" s="3">
         <v>1</v>
@@ -3409,16 +3411,16 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>43</v>
@@ -3428,24 +3430,24 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="J47" s="3">
-        <v>1</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>216</v>
+        <v>53</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>49</v>
@@ -3458,27 +3460,27 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>168</v>
+        <v>224</v>
       </c>
       <c r="J48" s="3">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>172</v>
+        <v>226</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>38</v>
@@ -3488,24 +3490,24 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>168</v>
+        <v>199</v>
       </c>
       <c r="J49" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>53</v>
+        <v>228</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>49</v>
@@ -3518,40 +3520,42 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>224</v>
+        <v>71</v>
       </c>
       <c r="J50" s="3">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>110</v>
+        <v>231</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>226</v>
+        <v>190</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F51" s="3"/>
+      <c r="F51" s="3" t="s">
+        <v>233</v>
+      </c>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>145</v>
+        <v>71</v>
       </c>
       <c r="J51" s="3">
         <v>0</v>
@@ -3559,73 +3563,73 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>110</v>
+        <v>225</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>229</v>
+        <v>152</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>166</v>
+        <v>37</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>168</v>
+        <v>199</v>
       </c>
       <c r="J52" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="J53" s="3">
-        <v>69</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>151</v>
+        <v>222</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>49</v>
@@ -3638,56 +3642,54 @@
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="J54" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>241</v>
+        <v>49</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F55" s="3" t="s">
-        <v>242</v>
-      </c>
+      <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>168</v>
+        <v>71</v>
       </c>
       <c r="J55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>49</v>
@@ -3700,27 +3702,27 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="J56" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>166</v>
+        <v>49</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>43</v>
@@ -3730,24 +3732,24 @@
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>168</v>
+        <v>71</v>
       </c>
       <c r="J57" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>49</v>
@@ -3760,13 +3762,13 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>251</v>
+        <v>71</v>
       </c>
       <c r="J58" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3774,10 +3776,10 @@
         <v>252</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>49</v>
@@ -3790,87 +3792,87 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J59" s="3">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>72</v>
+        <v>248</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>151</v>
+        <v>256</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>256</v>
+        <v>214</v>
       </c>
       <c r="J60" s="3">
-        <v>65</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>141</v>
+        <v>258</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>85</v>
+        <v>261</v>
       </c>
       <c r="J61" s="3">
-        <v>22</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>259</v>
+        <v>76</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>240</v>
+        <v>148</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>241</v>
+        <v>49</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>38</v>
@@ -3880,24 +3882,24 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>262</v>
+        <v>150</v>
       </c>
       <c r="J62" s="3">
-        <v>26</v>
+        <v>66</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>263</v>
+        <v>142</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>264</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>49</v>
@@ -3913,10 +3915,10 @@
         <v>265</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>208</v>
+        <v>89</v>
       </c>
       <c r="J63" s="3">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64">
@@ -3927,13 +3929,13 @@
         <v>267</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>241</v>
+        <v>49</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
@@ -3943,10 +3945,10 @@
         <v>268</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>193</v>
+        <v>261</v>
       </c>
       <c r="J64" s="3">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65">
@@ -3957,13 +3959,13 @@
         <v>270</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
@@ -3973,40 +3975,40 @@
         <v>271</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>145</v>
+        <v>272</v>
       </c>
       <c r="J65" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>173</v>
+        <v>275</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>116</v>
+        <v>276</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="J66" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
@@ -4014,10 +4016,10 @@
         <v>53</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>49</v>
@@ -4030,57 +4032,57 @@
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="J67" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>218</v>
+        <v>283</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="J68" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>281</v>
+        <v>114</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>43</v>
@@ -4090,10 +4092,10 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="J69" s="3">
         <v>1</v>
@@ -4101,13 +4103,13 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>283</v>
+        <v>114</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>49</v>
@@ -4120,10 +4122,10 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>99</v>
+        <v>214</v>
       </c>
       <c r="J70" s="3">
         <v>2</v>
@@ -4131,16 +4133,16 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>155</v>
+        <v>275</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>49</v>
+        <v>276</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>43</v>
@@ -4150,24 +4152,24 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>168</v>
+        <v>71</v>
       </c>
       <c r="J71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>110</v>
+        <v>291</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>49</v>
@@ -4180,54 +4182,56 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="J72" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>235</v>
+        <v>294</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>151</v>
+        <v>283</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F73" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>296</v>
+      </c>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>193</v>
+        <v>71</v>
       </c>
       <c r="J73" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>294</v>
+        <v>253</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>186</v>
+        <v>148</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>49</v>
@@ -4240,27 +4244,27 @@
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="J74" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>110</v>
+        <v>300</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>155</v>
+        <v>302</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>43</v>
@@ -4270,10 +4274,10 @@
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="J75" s="3">
         <v>1</v>
@@ -4281,29 +4285,29 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>205</v>
+        <v>283</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>206</v>
+        <v>120</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="J76" s="3">
         <v>6</v>
@@ -4311,16 +4315,16 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>240</v>
+        <v>148</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>241</v>
+        <v>49</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>43</v>
@@ -4330,27 +4334,27 @@
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>251</v>
+        <v>183</v>
       </c>
       <c r="J77" s="3">
-        <v>90</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>305</v>
+        <v>204</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>229</v>
+        <v>152</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>166</v>
+        <v>37</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>43</v>
@@ -4360,119 +4364,119 @@
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="J78" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>47</v>
+        <v>311</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>307</v>
+        <v>168</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F79" s="3" t="s">
-        <v>242</v>
-      </c>
+      <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="J79" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>151</v>
+        <v>275</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>49</v>
+        <v>276</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="J80" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>313</v>
+        <v>253</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>240</v>
+        <v>275</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>241</v>
+        <v>276</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F81" s="3"/>
+      <c r="F81" s="3" t="s">
+        <v>233</v>
+      </c>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>168</v>
+        <v>214</v>
       </c>
       <c r="J81" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>173</v>
+        <v>283</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>38</v>
@@ -4482,27 +4486,27 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J82" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>213</v>
+        <v>322</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>319</v>
+        <v>148</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>38</v>
@@ -4512,27 +4516,27 @@
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>208</v>
+        <v>103</v>
       </c>
       <c r="J83" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>203</v>
+        <v>324</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>151</v>
+        <v>283</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>38</v>
@@ -4542,40 +4546,40 @@
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>323</v>
+        <v>146</v>
       </c>
       <c r="J84" s="3">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>99</v>
+        <v>214</v>
       </c>
       <c r="J85" s="3">
         <v>2</v>
@@ -4583,46 +4587,46 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>328</v>
+        <v>161</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>145</v>
+        <v>331</v>
       </c>
       <c r="J86" s="3">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>332</v>
+        <v>190</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>43</v>
@@ -4632,27 +4636,27 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>168</v>
+        <v>214</v>
       </c>
       <c r="J87" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>186</v>
+        <v>283</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>43</v>
@@ -4665,24 +4669,24 @@
         <v>336</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>168</v>
+        <v>199</v>
       </c>
       <c r="J88" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>110</v>
+        <v>337</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>43</v>
@@ -4692,17 +4696,47 @@
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>168</v>
+        <v>71</v>
       </c>
       <c r="J89" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="J90" s="3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J89"/>
+  <autoFilter ref="A1:J90"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4792,6 +4826,7 @@
     <hyperlink ref="H87" r:id="rId86"/>
     <hyperlink ref="H88" r:id="rId87"/>
     <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4799,8 +4834,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="1" max="1" width="49" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -4833,10 +4868,10 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>141</v>
+        <v>68</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>142</v>
+        <v>64</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>49</v>
@@ -4847,18 +4882,18 @@
         <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>144</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -4866,18 +4901,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>110</v>
+        <v>228</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>169</v>
+        <v>229</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -4885,18 +4920,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>170</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>110</v>
+        <v>231</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>175</v>
+        <v>232</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -4904,18 +4939,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>176</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>110</v>
+        <v>228</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -4923,18 +4958,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>236</v>
+        <v>161</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -4942,18 +4977,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>270</v>
+        <v>235</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -4961,18 +4996,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>110</v>
+        <v>289</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>151</v>
+        <v>275</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -4985,13 +5020,13 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>229</v>
+        <v>283</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -4999,18 +5034,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>316</v>
+        <v>253</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5018,18 +5053,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>173</v>
+        <v>339</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5037,7 +5072,7 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -5067,47 +5102,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>242</v>
+        <v>296</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>344</v>
+        <v>233</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B6" s="3">
         <v>12</v>
@@ -5115,7 +5150,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B7" s="3">
         <v>12</v>
@@ -5123,7 +5158,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B8" s="3">
         <v>11</v>
@@ -5131,7 +5166,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B9" s="3">
         <v>11</v>
@@ -5139,7 +5174,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>143</v>
+        <v>351</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
@@ -5147,23 +5182,23 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>349</v>
+        <v>144</v>
       </c>
       <c r="B11" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
@@ -5171,7 +5206,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -5179,7 +5214,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5187,7 +5222,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5200,7 +5235,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5209,12 +5244,12 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B2" s="3">
         <v>4</v>
@@ -5222,15 +5257,15 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="B3" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5238,7 +5273,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5246,31 +5281,31 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>35</v>
+        <v>168</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>94</v>
+        <v>253</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>101</v>
+        <v>282</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>121</v>
+        <v>35</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5278,7 +5313,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>164</v>
+        <v>98</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5286,7 +5321,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>172</v>
+        <v>105</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5294,7 +5329,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>198</v>
+        <v>125</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5302,7 +5337,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>213</v>
+        <v>134</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5310,7 +5345,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5318,7 +5353,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5326,7 +5361,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5340,23 +5375,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="2">
@@ -5364,7 +5399,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C2" s="3">
         <v>16.8</v>
@@ -5392,13 +5427,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
       <c r="C4" s="3">
-        <v>8.8</v>
+        <v>10.1</v>
       </c>
       <c r="D4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -5406,13 +5441,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="C5" s="3">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="D5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -5420,10 +5455,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="C6" s="3">
-        <v>6.2</v>
+        <v>6.0</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -5434,10 +5469,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="C7" s="3">
-        <v>6.0</v>
+        <v>5.8</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -5448,10 +5483,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C8" s="3">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -5462,10 +5497,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="C9" s="3">
-        <v>5.3</v>
+        <v>5.0</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -5476,13 +5511,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>111</v>
+        <v>168</v>
       </c>
       <c r="C10" s="3">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="D10" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -5490,13 +5525,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>172</v>
+        <v>253</v>
       </c>
       <c r="C11" s="3">
-        <v>2.8</v>
+        <v>4.0</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -5504,13 +5539,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>198</v>
+        <v>161</v>
       </c>
       <c r="C12" s="3">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -5518,13 +5553,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>213</v>
+        <v>282</v>
       </c>
       <c r="C13" s="3">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -5532,13 +5567,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>239</v>
+        <v>115</v>
       </c>
       <c r="C14" s="3">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -5546,10 +5581,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>164</v>
+        <v>204</v>
       </c>
       <c r="C15" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -5560,7 +5595,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5586,15 +5621,15 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -5608,10 +5643,10 @@
         <v>43</v>
       </c>
       <c r="B3" s="3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="4">
@@ -5619,10 +5654,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -5641,7 +5676,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2">
@@ -5649,20 +5684,20 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B3" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>166</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
         <v>5</v>
@@ -5670,7 +5705,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>241</v>
+        <v>170</v>
       </c>
       <c r="B5" s="3">
         <v>5</v>
@@ -5678,7 +5713,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>37</v>
+        <v>276</v>
       </c>
       <c r="B6" s="3">
         <v>4</v>
@@ -5686,7 +5721,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5694,7 +5729,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5721,10 +5756,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5736,10 +5771,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5756,31 +5791,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3">
@@ -5788,31 +5823,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4">
@@ -5820,31 +5855,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>168</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5">
@@ -5852,31 +5887,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6">
@@ -5884,31 +5919,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>382</v>
+        <v>190</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>385</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7">
@@ -5916,31 +5951,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>386</v>
+        <v>304</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>387</v>
+        <v>161</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>186</v>
+        <v>148</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F7" s="3">
         <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>389</v>
+        <v>330</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8">
@@ -5948,31 +5983,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>272</v>
+        <v>85</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="F8" s="3">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>391</v>
+        <v>88</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9">
@@ -5980,31 +6015,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>81</v>
+        <v>389</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>76</v>
+        <v>390</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>77</v>
+        <v>391</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F9" s="3">
         <v>92</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>85</v>
+        <v>394</v>
       </c>
     </row>
     <row r="10">
@@ -6012,31 +6047,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>394</v>
+        <v>304</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="F10" s="3">
+        <v>88</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="F10" s="3">
-        <v>92</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>397</v>
-      </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>398</v>
+        <v>305</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>385</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -6044,31 +6079,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>272</v>
+        <v>396</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>273</v>
+        <v>333</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>173</v>
+        <v>275</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F11" s="3">
         <v>88</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>274</v>
+        <v>398</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>193</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -6076,31 +6111,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>400</v>
+        <v>42</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>401</v>
+        <v>35</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>240</v>
+        <v>36</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="F12" s="3">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>403</v>
+        <v>45</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>99</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
@@ -6108,31 +6143,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>42</v>
+        <v>400</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>35</v>
+        <v>401</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>36</v>
+        <v>148</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>392</v>
+        <v>366</v>
       </c>
       <c r="F13" s="3">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>45</v>
+        <v>403</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>46</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14">
@@ -6140,31 +6175,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="F14" s="3">
+        <v>60</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="F14" s="3">
-        <v>80</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>408</v>
-      </c>
       <c r="J14" s="3" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15">
@@ -6172,31 +6207,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="F15" s="3">
+        <v>52</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="F15" s="3">
-        <v>60</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>411</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="16">
@@ -6207,28 +6242,28 @@
         <v>412</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>257</v>
+        <v>413</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>151</v>
+        <v>414</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>392</v>
+        <v>415</v>
       </c>
       <c r="F16" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>168</v>
+        <v>418</v>
       </c>
     </row>
     <row r="17">
@@ -6236,31 +6271,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F17" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>419</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18">
@@ -6268,19 +6303,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>422</v>
+        <v>190</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>423</v>
+        <v>366</v>
       </c>
       <c r="F18" s="3">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>424</v>
@@ -6306,25 +6341,25 @@
         <v>428</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>182</v>
+        <v>429</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F19" s="3">
         <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -6332,31 +6367,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>431</v>
+        <v>267</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>186</v>
+        <v>148</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>365</v>
+        <v>415</v>
       </c>
       <c r="F20" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="21">
@@ -6364,31 +6399,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>435</v>
+        <v>419</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>436</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="F21" s="3">
+        <v>44</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="F21" s="3">
-        <v>48</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>439</v>
-      </c>
       <c r="J21" s="3" t="s">
-        <v>41</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W34.xlsx
+++ b/reports/devops-jobs-israel-2026-W34.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="460">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-20T06:58:46</t>
+    <t xml:space="preserve">2026-08-21T07:00:11</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -195,6 +195,24 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior Full Stack Developer – Core Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Postgres, MySQL, Kafka, RabbitMQ, Crossplane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/8143427/?gh_jid=8143427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-21</t>
+  </si>
+  <si>
     <t xml:space="preserve">Developer Advocate</t>
   </si>
   <si>
@@ -375,6 +393,18 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
   </si>
   <si>
+    <t xml:space="preserve">Director of Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yotpo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
+  </si>
+  <si>
     <t xml:space="preserve">Riskified</t>
   </si>
   <si>
@@ -453,21 +483,24 @@
     <t xml:space="preserve">Optimove</t>
   </si>
   <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-19</t>
   </si>
   <si>
+    <t xml:space="preserve">Vetric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vetric-4455613930</t>
+  </si>
+  <si>
     <t xml:space="preserve">Connecteam</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
   </si>
   <si>
@@ -489,21 +522,9 @@
     <t xml:space="preserve">CommBox</t>
   </si>
   <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4456470553</t>
   </si>
   <si>
-    <t xml:space="preserve">Agora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-agora-4451343371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-10</t>
-  </si>
-  <si>
     <t xml:space="preserve">Paragon</t>
   </si>
   <si>
@@ -513,6 +534,120 @@
     <t xml:space="preserve">2026-05-25</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4442854342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4452584141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4446898048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gini-apps-4455709981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allpha Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allpha-innovation-4454255466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simplex 3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-simplex-3d-4452264625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appcharge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-appcharge-4454760249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-descope-4431665949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wiz</t>
   </si>
   <si>
@@ -522,46 +657,280 @@
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4442854342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4452584141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gini-apps-4455709981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earnix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualcomm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Startup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stealth-startup-4455619482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-skai-4427485314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagry | Autonomous Driving</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-imagry-autonomous-driving-4452259211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Team lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-compie-technologies-4455300779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, AI Agent Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-4442909711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eyesAtop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-eyesatop-4454764581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441571472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or HaNer, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4452238627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4454269739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Data Infrastructure Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-team-leader-at-evoke-4443982712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cyera-4456176236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-planck-4455682332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer – Kubernetes &amp; AI - 4664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bynet Software Systems Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%E2%80%93-kubernetes-ai-4664-at-bynet-software-systems-ltd-4454492747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (37386)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37386-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4456717268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal/Senior ML Platform Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-senior-ml-platform-engineer-cortex-at-palo-alto-networks-4433913015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4455938126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend &amp; Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-data-platform-engineer-at-loora-2147625360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
   </si>
   <si>
     <t xml:space="preserve">Transmit Security</t>
@@ -570,7 +939,28 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16</t>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-jobgether-4454997118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Lead - DevOps And Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-lead-devops-and-cloud-at-terasky-4452249308</t>
   </si>
   <si>
     <t xml:space="preserve">Sr. Principal, DevOps</t>
@@ -588,649 +978,313 @@
     <t xml:space="preserve">2026-07-08</t>
   </si>
   <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-descope-4431665949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tonkean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-tonkean-4452977126</t>
+    <t xml:space="preserve">Senior Lead Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-infrastructure-engineer-at-sela-4454743727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devsecops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-dialog-4452580295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4454251693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-infrastructure-engineer-at-shavit-software-4455295099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identity &amp; Authentication Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/identity-authentication-infrastructure-engineer-at-logica-it-4452547813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harish, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-system-engineer-at-comblack-4456486918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Full Stack Developer - Data Loss Prevention Cloud Service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-full-stack-developer-data-loss-prevention-cloud-service-at-check-point-software-4455339838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4455765409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterfall Security Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4454032601</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-14</t>
   </si>
   <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allpha Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allpha-innovation-4454255466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earnix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer, NCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-ai-4450816877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cyera-4456176236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devsecops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-dialog-4452580295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-4453261687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Data Infrastructure Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-team-leader-at-evoke-4443982712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antidote Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-antidote-health-4452991835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eyesAtop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-eyesatop-4454764581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-skai-4427485314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or HaNer, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4452238627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-infrastructure-engineer-at-comblack-4455291083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appcharge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-appcharge-4454760249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simplex 3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-simplex-3d-4452264625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Streaming Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-streaming-platform-engineer-at-nuvei-4455192546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer – Kubernetes &amp; AI - 4664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bynet Software Systems Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%E2%80%93-kubernetes-ai-4664-at-bynet-software-systems-ltd-4454492747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4455938126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4454032601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend &amp; Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-data-platform-engineer-at-loora-2147625360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4454251693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Lead - DevOps And Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-lead-devops-and-cloud-at-terasky-4452249308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Staff DevOps Engineer - Cloud Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-cloud-security-at-palo-alto-networks-4450813194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Lead Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-infrastructure-engineer-at-sela-4454743727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4455193277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Administrator</t>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Developer - SAP BTP - CCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-developer-sap-btp-ccs-at-sap-4343365945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Environment Support Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">abra</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-at-abra-4454749355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-infrastructure-engineer-at-shavit-software-4455295099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identity &amp; Authentication Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/identity-authentication-infrastructure-engineer-at-logica-it-4452547813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-comblack-4454021597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-jobgether-4454997118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4454269739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Full Stack Developer - Data Loss Prevention Cloud Service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-full-stack-developer-data-loss-prevention-cloud-service-at-check-point-software-4455339838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4455765409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterfall Security Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-at-logica-it-4452227142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
   </si>
   <si>
     <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
@@ -1257,25 +1311,16 @@
     <t xml:space="preserve">2026-06-30</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">etoro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
+    <t xml:space="preserve">IT Operations Engineer I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
   </si>
   <si>
     <t xml:space="preserve">System Administrator</t>
@@ -1302,42 +1347,6 @@
     <t xml:space="preserve">2026-07-31</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator for Computing Qual (testing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-for-computing-qual-testing-at-applied-materials-israel-4449806027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist – MENTEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4455175909</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
@@ -1350,22 +1359,19 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
     <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1525,7 +1531,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1533,7 +1539,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
@@ -1541,7 +1547,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1113</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="10">
@@ -1613,7 +1619,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
@@ -1621,7 +1627,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1640,36 +1646,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>415</v>
+        <v>370</v>
       </c>
       <c r="B2" s="3">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>366</v>
+        <v>416</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1677,7 +1683,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1690,24 +1696,24 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B2" s="3">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -1715,28 +1721,28 @@
         <v>353</v>
       </c>
       <c r="B3" s="3">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>350</v>
+        <v>445</v>
       </c>
       <c r="B4" s="3">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B5" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>443</v>
+        <v>351</v>
       </c>
       <c r="B6" s="3">
         <v>22</v>
@@ -1744,7 +1750,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>444</v>
+        <v>356</v>
       </c>
       <c r="B7" s="3">
         <v>21</v>
@@ -1752,74 +1758,74 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B9" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B10" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>447</v>
+        <v>350</v>
       </c>
       <c r="B12" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>352</v>
+        <v>449</v>
       </c>
       <c r="B13" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>345</v>
+        <v>286</v>
       </c>
       <c r="B14" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="B15" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B16" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1844,13 +1850,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="2">
@@ -1858,13 +1864,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3">
-        <v>12.5</v>
+        <v>24.5</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1876,85 +1882,85 @@
         <v>71</v>
       </c>
       <c r="C3" s="3">
-        <v>34.7</v>
+        <v>37.1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.3</v>
+        <v>7.7</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>35.1</v>
+        <v>33.5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>20.3</v>
+        <v>17.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.2</v>
+        <v>15.6</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1966,7 +1972,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2038,7 +2044,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2070,7 +2076,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -2102,7 +2108,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5">
@@ -2134,7 +2140,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -2166,7 +2172,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -2183,7 +2189,7 @@
         <v>49</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>61</v>
@@ -2195,50 +2201,50 @@
         <v>62</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="J7" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>67</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>49</v>
@@ -2250,27 +2256,27 @@
         <v>38</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J9" s="3">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>49</v>
@@ -2282,27 +2288,27 @@
         <v>38</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J10" s="3">
-        <v>84</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>49</v>
@@ -2314,30 +2320,30 @@
         <v>38</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="J11" s="3">
-        <v>67</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>49</v>
@@ -2346,19 +2352,19 @@
         <v>38</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="J12" s="3">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -2366,60 +2372,60 @@
         <v>85</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J13" s="3">
-        <v>23</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="J14" s="3">
         <v>24</v>
@@ -2427,13 +2433,13 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>49</v>
@@ -2442,30 +2448,30 @@
         <v>38</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="J15" s="3">
-        <v>83</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>49</v>
@@ -2474,16 +2480,16 @@
         <v>38</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="J16" s="3">
         <v>84</v>
@@ -2491,13 +2497,13 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>49</v>
@@ -2506,36 +2512,36 @@
         <v>38</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="J17" s="3">
-        <v>3</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="C18" s="3" t="s">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>107</v>
@@ -2550,7 +2556,7 @@
         <v>109</v>
       </c>
       <c r="J18" s="3">
-        <v>46</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -2558,60 +2564,60 @@
         <v>110</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J19" s="3">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="J20" s="3">
         <v>9</v>
@@ -2619,34 +2625,34 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c r="J21" s="3">
-        <v>69</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -2657,13 +2663,13 @@
         <v>125</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>126</v>
@@ -2675,53 +2681,53 @@
         <v>127</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="J22" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="D23" s="3" t="s">
-        <v>49</v>
+        <v>130</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J23" s="3">
-        <v>16</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>49</v>
@@ -2742,7 +2748,7 @@
         <v>138</v>
       </c>
       <c r="J24" s="3">
-        <v>74</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -2750,10 +2756,10 @@
         <v>139</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>49</v>
@@ -2771,113 +2777,117 @@
         <v>141</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="J25" s="3">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J26" s="3">
-        <v>1</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>150</v>
+      </c>
       <c r="G27" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>150</v>
+        <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>66</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>152</v>
+        <v>49</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F28" s="3"/>
+      <c r="F28" s="3" t="s">
+        <v>126</v>
+      </c>
       <c r="G28" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J28" s="3">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>49</v>
@@ -2890,10 +2900,10 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -2901,13 +2911,13 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>49</v>
@@ -2920,27 +2930,27 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J30" s="3">
-        <v>10</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>43</v>
@@ -2950,24 +2960,24 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J31" s="3">
-        <v>87</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>148</v>
+        <v>60</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>49</v>
@@ -2980,27 +2990,27 @@
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="J32" s="3">
-        <v>88</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>167</v>
+        <v>120</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>170</v>
+        <v>49</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>43</v>
@@ -3010,27 +3020,27 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>89</v>
+        <v>170</v>
       </c>
       <c r="J33" s="3">
-        <v>23</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>172</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>49</v>
+        <v>174</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>43</v>
@@ -3040,24 +3050,24 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>146</v>
+        <v>95</v>
       </c>
       <c r="J34" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>49</v>
@@ -3070,30 +3080,30 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="J35" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>176</v>
+        <v>120</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>170</v>
+        <v>37</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
@@ -3103,171 +3113,171 @@
         <v>179</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>180</v>
+        <v>138</v>
       </c>
       <c r="J36" s="3">
-        <v>85</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="J37" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>184</v>
+        <v>120</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>120</v>
+        <v>174</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J38" s="3">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>114</v>
+        <v>186</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>49</v>
+        <v>174</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J39" s="3">
-        <v>57</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="D40" s="3" t="s">
-        <v>195</v>
+        <v>49</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="J40" s="3">
-        <v>88</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>53</v>
+        <v>120</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="J41" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>49</v>
@@ -3280,87 +3290,87 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="J42" s="3">
-        <v>31</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>203</v>
+        <v>120</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>148</v>
+        <v>201</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="J43" s="3">
-        <v>48</v>
+        <v>67</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>208</v>
+        <v>172</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="J44" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>170</v>
+        <v>49</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>43</v>
@@ -3370,24 +3380,24 @@
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="J45" s="3">
-        <v>2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>215</v>
+        <v>120</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>49</v>
@@ -3400,43 +3410,43 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>146</v>
+        <v>211</v>
       </c>
       <c r="J46" s="3">
-        <v>1</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>114</v>
+        <v>212</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>49</v>
+        <v>215</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>150</v>
+        <v>217</v>
       </c>
       <c r="J47" s="3">
-        <v>66</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
@@ -3444,10 +3454,10 @@
         <v>53</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>49</v>
@@ -3460,57 +3470,57 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="J48" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>49</v>
+        <v>130</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="J49" s="3">
-        <v>6</v>
+        <v>71</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>228</v>
+        <v>53</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>190</v>
+        <v>227</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>49</v>
+        <v>130</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>38</v>
@@ -3520,10 +3530,10 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="J50" s="3">
         <v>0</v>
@@ -3531,48 +3541,46 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H51" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>234</v>
-      </c>
       <c r="I51" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="J51" s="3">
         <v>71</v>
-      </c>
-      <c r="J51" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>38</v>
@@ -3582,27 +3590,27 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>199</v>
+        <v>115</v>
       </c>
       <c r="J52" s="3">
-        <v>6</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>237</v>
+        <v>120</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>156</v>
+        <v>236</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>49</v>
+        <v>174</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>43</v>
@@ -3612,24 +3620,24 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="J53" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>49</v>
@@ -3642,24 +3650,24 @@
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="J54" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>243</v>
+        <v>178</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>49</v>
@@ -3672,24 +3680,24 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>71</v>
+        <v>165</v>
       </c>
       <c r="J55" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>148</v>
+        <v>193</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>49</v>
@@ -3702,54 +3710,54 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="J56" s="3">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>161</v>
+        <v>247</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>71</v>
+        <v>211</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>250</v>
+        <v>82</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>49</v>
@@ -3762,27 +3770,27 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>71</v>
+        <v>161</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="D59" s="3" t="s">
-        <v>49</v>
+        <v>254</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>38</v>
@@ -3792,90 +3800,90 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>166</v>
+        <v>256</v>
       </c>
       <c r="J59" s="3">
-        <v>88</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>256</v>
+        <v>157</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="J60" s="3">
-        <v>2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>259</v>
+        <v>168</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>261</v>
+        <v>77</v>
       </c>
       <c r="J61" s="3">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>262</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
@@ -3885,24 +3893,24 @@
         <v>263</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="J62" s="3">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>142</v>
+        <v>260</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>264</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>148</v>
+        <v>265</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>49</v>
+        <v>130</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>43</v>
@@ -3912,30 +3920,30 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>89</v>
+        <v>185</v>
       </c>
       <c r="J63" s="3">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>267</v>
+        <v>178</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
@@ -3945,54 +3953,54 @@
         <v>268</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>261</v>
+        <v>77</v>
       </c>
       <c r="J64" s="3">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="C65" s="3" t="s">
-        <v>148</v>
+        <v>60</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="I65" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="I65" s="3" t="s">
-        <v>272</v>
-      </c>
       <c r="J65" s="3">
-        <v>70</v>
+        <v>32</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>273</v>
+        <v>53</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>275</v>
+        <v>206</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>276</v>
+        <v>49</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>38</v>
@@ -4002,177 +4010,179 @@
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="J66" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>53</v>
+        <v>274</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>148</v>
+        <v>60</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>280</v>
+        <v>185</v>
       </c>
       <c r="J67" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>281</v>
+        <v>243</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>283</v>
+        <v>206</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>214</v>
+        <v>77</v>
       </c>
       <c r="J68" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="J69" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>214</v>
+        <v>283</v>
       </c>
       <c r="J70" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>275</v>
+        <v>227</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>276</v>
+        <v>130</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F71" s="3"/>
+      <c r="F71" s="3" t="s">
+        <v>286</v>
+      </c>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="J71" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>148</v>
+        <v>227</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>49</v>
+        <v>130</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>43</v>
@@ -4182,56 +4192,54 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="J72" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>295</v>
+        <v>247</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>283</v>
+        <v>157</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>296</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="J73" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>49</v>
@@ -4244,10 +4252,10 @@
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="J74" s="3">
         <v>0</v>
@@ -4255,46 +4263,46 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>301</v>
+        <v>172</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>302</v>
+        <v>214</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>170</v>
+        <v>215</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>146</v>
+        <v>211</v>
       </c>
       <c r="J75" s="3">
-        <v>1</v>
+        <v>89</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>283</v>
+        <v>236</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>120</v>
+        <v>174</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>43</v>
@@ -4304,24 +4312,24 @@
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>199</v>
+        <v>155</v>
       </c>
       <c r="J76" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>49</v>
@@ -4334,149 +4342,147 @@
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>183</v>
+        <v>303</v>
       </c>
       <c r="J77" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>309</v>
+        <v>149</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>204</v>
+        <v>304</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>214</v>
+        <v>303</v>
       </c>
       <c r="J78" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>311</v>
+        <v>53</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>168</v>
+        <v>306</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>169</v>
+        <v>253</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>170</v>
+        <v>254</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>214</v>
+        <v>109</v>
       </c>
       <c r="J79" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>275</v>
+        <v>310</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>276</v>
+        <v>130</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>214</v>
+        <v>77</v>
       </c>
       <c r="J80" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="3" t="s">
-        <v>275</v>
-      </c>
       <c r="D81" s="3" t="s">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>233</v>
-      </c>
+      <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="J81" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>283</v>
+        <v>316</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>38</v>
@@ -4486,27 +4492,27 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>146</v>
+        <v>318</v>
       </c>
       <c r="J82" s="3">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>148</v>
+        <v>227</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>49</v>
+        <v>130</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>38</v>
@@ -4516,40 +4522,42 @@
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="J83" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F84" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="G84" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H84" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="C84" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>326</v>
-      </c>
       <c r="I84" s="3" t="s">
-        <v>146</v>
+        <v>77</v>
       </c>
       <c r="J84" s="3">
         <v>1</v>
@@ -4557,16 +4565,16 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="C85" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="C85" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="D85" s="3" t="s">
-        <v>49</v>
+        <v>130</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>43</v>
@@ -4579,21 +4587,21 @@
         <v>329</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>214</v>
+        <v>63</v>
       </c>
       <c r="J85" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>49</v>
@@ -4606,27 +4614,27 @@
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J86" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>43</v>
@@ -4636,27 +4644,27 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="J87" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>282</v>
+        <v>337</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>283</v>
+        <v>206</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>43</v>
@@ -4666,27 +4674,27 @@
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="J88" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>339</v>
+        <v>206</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>43</v>
@@ -4696,43 +4704,43 @@
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>71</v>
+        <v>185</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>53</v>
+        <v>342</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>190</v>
+        <v>344</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>49</v>
+        <v>174</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>214</v>
+        <v>63</v>
       </c>
       <c r="J90" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4834,8 +4842,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="1" max="1" width="48" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -4868,13 +4876,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -4882,37 +4890,37 @@
         <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>156</v>
+        <v>49</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>157</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>228</v>
+        <v>120</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>229</v>
+        <v>156</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -4920,18 +4928,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>230</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>231</v>
+        <v>53</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>190</v>
+        <v>227</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -4939,18 +4947,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>243</v>
+        <v>279</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>222</v>
+        <v>157</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -4958,18 +4966,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>244</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>248</v>
+        <v>288</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>161</v>
+        <v>289</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>148</v>
+        <v>227</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -4977,18 +4985,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>250</v>
+        <v>293</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -4996,18 +5004,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>251</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>289</v>
+        <v>326</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>267</v>
+        <v>327</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>275</v>
+        <v>328</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5015,18 +5023,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>290</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>294</v>
+        <v>342</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>295</v>
+        <v>343</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>283</v>
+        <v>344</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5034,49 +5042,11 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12"/>
+  <autoFilter ref="A1:G10"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5087,8 +5057,6 @@
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5102,55 +5070,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="B4" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>233</v>
+        <v>324</v>
       </c>
       <c r="B5" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B6" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B7" s="3">
         <v>12</v>
@@ -5158,7 +5126,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B8" s="3">
         <v>11</v>
@@ -5166,7 +5134,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B9" s="3">
         <v>11</v>
@@ -5174,15 +5142,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>351</v>
+        <v>126</v>
       </c>
       <c r="B10" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>144</v>
+        <v>354</v>
       </c>
       <c r="B11" s="3">
         <v>9</v>
@@ -5190,15 +5158,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
@@ -5206,7 +5174,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -5214,7 +5182,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5222,7 +5190,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5244,12 +5212,12 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B2" s="3">
         <v>4</v>
@@ -5257,7 +5225,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B3" s="3">
         <v>4</v>
@@ -5273,7 +5241,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5281,7 +5249,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5289,7 +5257,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>253</v>
+        <v>178</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5297,7 +5265,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>282</v>
+        <v>247</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5313,7 +5281,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5321,7 +5289,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5329,7 +5297,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5337,7 +5305,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5345,7 +5313,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>204</v>
+        <v>306</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5353,18 +5321,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>235</v>
+        <v>59</v>
       </c>
       <c r="B15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>267</v>
+        <v>65</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5382,16 +5350,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2">
@@ -5399,7 +5367,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C2" s="3">
         <v>16.8</v>
@@ -5427,7 +5395,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C4" s="3">
         <v>10.1</v>
@@ -5455,7 +5423,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C6" s="3">
         <v>6.0</v>
@@ -5469,7 +5437,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C7" s="3">
         <v>5.8</v>
@@ -5483,7 +5451,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C8" s="3">
         <v>5.3</v>
@@ -5497,7 +5465,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="C9" s="3">
         <v>5.0</v>
@@ -5511,7 +5479,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C10" s="3">
         <v>4.2</v>
@@ -5525,10 +5493,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>253</v>
+        <v>178</v>
       </c>
       <c r="C11" s="3">
-        <v>4.0</v>
+        <v>4.2</v>
       </c>
       <c r="D11" s="3">
         <v>3</v>
@@ -5539,7 +5507,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="C12" s="3">
         <v>3.6</v>
@@ -5553,7 +5521,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>282</v>
+        <v>247</v>
       </c>
       <c r="C13" s="3">
         <v>3.6</v>
@@ -5567,7 +5535,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C14" s="3">
         <v>2.9</v>
@@ -5581,13 +5549,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>204</v>
+        <v>59</v>
       </c>
       <c r="C15" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -5595,7 +5563,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>235</v>
+        <v>306</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5621,15 +5589,15 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -5643,10 +5611,10 @@
         <v>43</v>
       </c>
       <c r="B3" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="4">
@@ -5654,10 +5622,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -5676,7 +5644,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2">
@@ -5684,12 +5652,12 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B3" s="3">
         <v>10</v>
@@ -5697,15 +5665,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>174</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>170</v>
+        <v>37</v>
       </c>
       <c r="B5" s="3">
         <v>5</v>
@@ -5713,15 +5681,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="B6" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5729,7 +5697,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5756,10 +5724,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5771,10 +5739,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5791,31 +5759,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3">
@@ -5823,31 +5791,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>373</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4">
@@ -5855,31 +5823,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>214</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5">
@@ -5887,31 +5855,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>156</v>
+        <v>60</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>166</v>
+        <v>386</v>
       </c>
     </row>
     <row r="6">
@@ -5919,31 +5887,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>146</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7">
@@ -5951,31 +5919,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>304</v>
+        <v>391</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>161</v>
+        <v>392</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>148</v>
+        <v>60</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F7" s="3">
         <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>330</v>
+        <v>394</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>123</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8">
@@ -5983,31 +5951,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>85</v>
+        <v>395</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>80</v>
+        <v>396</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="F8" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>88</v>
+        <v>398</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>89</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9">
@@ -6015,31 +5983,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>389</v>
+        <v>330</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>390</v>
+        <v>168</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>391</v>
+        <v>157</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="F9" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>393</v>
+        <v>331</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>394</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
@@ -6047,31 +6015,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>304</v>
+        <v>91</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>282</v>
+        <v>86</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>283</v>
+        <v>87</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="F10" s="3">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>305</v>
+        <v>94</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
@@ -6079,31 +6047,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>333</v>
+        <v>402</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>275</v>
+        <v>403</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="F11" s="3">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>103</v>
+        <v>406</v>
       </c>
     </row>
     <row r="12">
@@ -6111,31 +6079,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>42</v>
+        <v>330</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>35</v>
+        <v>343</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>36</v>
+        <v>227</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="F12" s="3">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>45</v>
+        <v>408</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>46</v>
+        <v>409</v>
       </c>
     </row>
     <row r="13">
@@ -6143,31 +6111,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>400</v>
+        <v>42</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>401</v>
+        <v>35</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>148</v>
+        <v>36</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="F13" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>403</v>
+        <v>45</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>214</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
@@ -6175,31 +6143,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>35</v>
+        <v>378</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>36</v>
+        <v>163</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="F14" s="3">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>154</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -6207,31 +6175,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>148</v>
+        <v>227</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>366</v>
+        <v>416</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>411</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16">
@@ -6239,31 +6207,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>413</v>
+        <v>298</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>414</v>
+        <v>236</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>415</v>
+        <v>379</v>
       </c>
       <c r="F16" s="3">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>418</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17">
@@ -6271,31 +6239,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>420</v>
+        <v>35</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>186</v>
+        <v>36</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F17" s="3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>113</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18">
@@ -6303,31 +6271,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F18" s="3">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="19">
@@ -6335,31 +6303,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>429</v>
+        <v>193</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F19" s="3">
         <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20">
@@ -6367,31 +6335,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>267</v>
+        <v>435</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>148</v>
+        <v>316</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>415</v>
+        <v>370</v>
       </c>
       <c r="F20" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>435</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21">
@@ -6399,31 +6367,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F21" s="3">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>214</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W34.xlsx
+++ b/reports/devops-jobs-israel-2026-W34.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="470">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-21T07:00:11</t>
+    <t xml:space="preserve">2026-08-23T06:54:30</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -243,6 +243,18 @@
     <t xml:space="preserve">2026-06-14</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior DevOps Engineer- for Adi Davidovic's team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4700779006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-23</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior DevSecOps Manager</t>
   </si>
   <si>
@@ -507,106 +519,373 @@
     <t xml:space="preserve">2026-06-15</t>
   </si>
   <si>
-    <t xml:space="preserve">AllCloud</t>
+    <t xml:space="preserve">CommBox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4456470553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4452584141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4442854342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
   </si>
   <si>
     <t xml:space="preserve">Raanana, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4443370175</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4446898048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gini-apps-4455709981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (37386)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37386-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4456717268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Principal, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-descope-4431665949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allpha Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allpha-innovation-4454255466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - KubeOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kubeops-team-at-wix-4453083488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earnix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Startup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stealth-startup-4455619482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-skai-4427485314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yad2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-yad2-4439486812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagry | Autonomous Driving</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-imagry-autonomous-driving-4452259211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Team lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-compie-technologies-4455300779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, AI Agent Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-4442909711</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-22</t>
   </si>
   <si>
-    <t xml:space="preserve">CommBox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4456470553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4442854342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4452584141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4446898048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gini-apps-4455709981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allpha Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allpha-innovation-4454255466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOLL Medical Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eyesAtop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-eyesatop-4454764581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4442990421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4454269739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Data Infrastructure Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-team-leader-at-evoke-4443982712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cyera-4456176236</t>
   </si>
   <si>
     <t xml:space="preserve">Simplex 3D</t>
@@ -615,37 +894,103 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-simplex-3d-4452264625</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Engineer – Kubernetes &amp; AI - 4664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bynet Software Systems Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%E2%80%93-kubernetes-ai-4664-at-bynet-software-systems-ltd-4454492747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal/Senior ML Platform Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-senior-ml-platform-engineer-cortex-at-palo-alto-networks-4433913015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4455068343</t>
+  </si>
+  <si>
     <t xml:space="preserve">Appcharge</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-appcharge-4454760249</t>
   </si>
   <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-descope-4431665949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-jobgether-4454997118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4454251693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Lead Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-infrastructure-engineer-at-sela-4454743727</t>
   </si>
   <si>
     <t xml:space="preserve">Wiz</t>
@@ -654,166 +999,61 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earnix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualcomm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stealth-startup-4455619482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-skai-4427485314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imagry | Autonomous Driving</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-imagry-autonomous-driving-4452259211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Team lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-compie-technologies-4455300779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, AI Agent Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-4442909711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eyesAtop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-eyesatop-4454764581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441571472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
+    <t xml:space="preserve">Devsecops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-dialog-4452580295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer (37375)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-37375-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4456729325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4455193277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-at-abra-4454749355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-infrastructure-engineer-at-shavit-software-4455295099</t>
   </si>
   <si>
     <t xml:space="preserve">Or HaNer, South District, Israel</t>
@@ -822,405 +1062,177 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4452238627</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4454269739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Data Infrastructure Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-team-leader-at-evoke-4443982712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cyera-4456176236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-planck-4455682332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer – Kubernetes &amp; AI - 4664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bynet Software Systems Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%E2%80%93-kubernetes-ai-4664-at-bynet-software-systems-ltd-4454492747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (37386)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37386-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4456717268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal/Senior ML Platform Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-senior-ml-platform-engineer-cortex-at-palo-alto-networks-4433913015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4455938126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend &amp; Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-data-platform-engineer-at-loora-2147625360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-jobgether-4454997118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Lead - DevOps And Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-lead-devops-and-cloud-at-terasky-4452249308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Principal, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Lead Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-infrastructure-engineer-at-sela-4454743727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devsecops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-dialog-4452580295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
+    <t xml:space="preserve">DevOps / Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-tairc-4453497245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harish, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-system-engineer-at-comblack-4456486918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4455765409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
   </si>
   <si>
     <t xml:space="preserve">System Engineer</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4454251693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-infrastructure-engineer-at-shavit-software-4455295099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identity &amp; Authentication Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/identity-authentication-infrastructure-engineer-at-logica-it-4452547813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harish, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-system-engineer-at-comblack-4456486918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Full Stack Developer - Data Loss Prevention Cloud Service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-full-stack-developer-data-loss-prevention-cloud-service-at-check-point-software-4455339838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4455765409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -1242,33 +1254,12 @@
     <t xml:space="preserve">2026-08-03</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4454032601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">Student Developer - SAP BTP - CCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-developer-sap-btp-ccs-at-sap-4343365945</t>
-  </si>
-  <si>
     <t xml:space="preserve">Test Environment Support Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
@@ -1278,15 +1269,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
   </si>
   <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
   </si>
   <si>
@@ -1311,18 +1293,6 @@
     <t xml:space="preserve">2026-06-30</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Operations Engineer I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
@@ -1335,33 +1305,93 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4451682760</t>
   </si>
   <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist – MENTEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyantis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-operations-student-nights-weekend-shifts-at-voyantis-4440108780</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiliot</t>
   </si>
   <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
+    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
@@ -1371,7 +1401,7 @@
     <t xml:space="preserve">Git</t>
   </si>
   <si>
-    <t xml:space="preserve">Virtualization</t>
+    <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1523,7 +1553,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7">
@@ -1531,7 +1561,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1539,7 +1569,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -1547,7 +1577,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1122</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="10">
@@ -1619,7 +1649,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -1627,7 +1657,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1646,20 +1676,20 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B3" s="3">
         <v>16</v>
@@ -1667,15 +1697,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B4" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>374</v>
+        <v>443</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1683,7 +1713,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>442</v>
+        <v>386</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1696,21 +1726,21 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="B2" s="3">
         <v>32</v>
@@ -1718,95 +1748,95 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>353</v>
+        <v>455</v>
       </c>
       <c r="B3" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>445</v>
+        <v>360</v>
       </c>
       <c r="B4" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>446</v>
+        <v>364</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>351</v>
+        <v>456</v>
       </c>
       <c r="B6" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B7" s="3">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="B8" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="B9" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="B10" s="3">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B11" s="3">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>350</v>
+        <v>459</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>449</v>
+        <v>357</v>
       </c>
       <c r="B13" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>286</v>
+        <v>460</v>
       </c>
       <c r="B14" s="3">
         <v>10</v>
@@ -1814,18 +1844,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>354</v>
+        <v>293</v>
       </c>
       <c r="B15" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>450</v>
+        <v>361</v>
       </c>
       <c r="B16" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1850,13 +1880,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
     </row>
     <row r="2">
@@ -1864,13 +1894,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="3">
-        <v>24.5</v>
+        <v>14.1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1882,85 +1912,85 @@
         <v>71</v>
       </c>
       <c r="C3" s="3">
-        <v>37.1</v>
+        <v>35.7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>7.7</v>
+        <v>8.7</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>33.5</v>
+        <v>32.2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>17.0</v>
+        <v>17.7</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>15.6</v>
+        <v>17.3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2044,7 +2074,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -2076,7 +2106,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -2108,7 +2138,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="3">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5">
@@ -2140,7 +2170,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -2172,7 +2202,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -2204,7 +2234,7 @@
         <v>63</v>
       </c>
       <c r="J7" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2236,7 +2266,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -2268,7 +2298,7 @@
         <v>73</v>
       </c>
       <c r="J9" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -2300,7 +2330,7 @@
         <v>77</v>
       </c>
       <c r="J10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2332,7 +2362,7 @@
         <v>81</v>
       </c>
       <c r="J11" s="3">
-        <v>85</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -2361,21 +2391,21 @@
         <v>84</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="J12" s="3">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>49</v>
@@ -2384,68 +2414,68 @@
         <v>38</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="J13" s="3">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="D14" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="J14" s="3">
-        <v>24</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>97</v>
@@ -2457,21 +2487,21 @@
         <v>98</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="J15" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>49</v>
@@ -2480,19 +2510,19 @@
         <v>38</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>102</v>
+        <v>46</v>
       </c>
       <c r="J16" s="3">
-        <v>84</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17">
@@ -2500,10 +2530,10 @@
         <v>103</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>49</v>
@@ -2512,30 +2542,30 @@
         <v>38</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H17" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="J17" s="3">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>49</v>
@@ -2544,65 +2574,65 @@
         <v>38</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="J18" s="3">
-        <v>4</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>113</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J19" s="3">
-        <v>47</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="D20" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>43</v>
@@ -2620,7 +2650,7 @@
         <v>119</v>
       </c>
       <c r="J20" s="3">
-        <v>9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -2628,31 +2658,31 @@
         <v>120</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J21" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
@@ -2681,85 +2711,85 @@
         <v>127</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>47</v>
+        <v>128</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>133</v>
+        <v>63</v>
       </c>
       <c r="J23" s="3">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="E24" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="J24" s="3">
-        <v>22</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="C25" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>49</v>
@@ -2780,7 +2810,7 @@
         <v>142</v>
       </c>
       <c r="J25" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
@@ -2788,10 +2818,10 @@
         <v>143</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>145</v>
+        <v>91</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>49</v>
@@ -2800,30 +2830,30 @@
         <v>38</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J26" s="3">
-        <v>75</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>49</v>
@@ -2841,53 +2871,53 @@
         <v>151</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>41</v>
+        <v>152</v>
       </c>
       <c r="J27" s="3">
-        <v>10</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>49</v>
+        <v>149</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>155</v>
+        <v>41</v>
       </c>
       <c r="J28" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>157</v>
+        <v>49</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>49</v>
@@ -2895,29 +2925,31 @@
       <c r="E29" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F29" s="3"/>
+      <c r="F29" s="3" t="s">
+        <v>130</v>
+      </c>
       <c r="G29" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>158</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>63</v>
+        <v>159</v>
       </c>
       <c r="J29" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>49</v>
@@ -2930,27 +2962,27 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>161</v>
+        <v>63</v>
       </c>
       <c r="J30" s="3">
-        <v>67</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>43</v>
@@ -2966,12 +2998,12 @@
         <v>165</v>
       </c>
       <c r="J31" s="3">
-        <v>30</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>166</v>
@@ -2993,21 +3025,21 @@
         <v>167</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J32" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>49</v>
@@ -3026,21 +3058,21 @@
         <v>170</v>
       </c>
       <c r="J33" s="3">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>172</v>
-      </c>
       <c r="C34" s="3" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>174</v>
+        <v>49</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>43</v>
@@ -3050,24 +3082,24 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>95</v>
+        <v>173</v>
       </c>
       <c r="J34" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>49</v>
@@ -3080,27 +3112,27 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="J35" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>120</v>
+        <v>176</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="D36" s="3" t="s">
-        <v>37</v>
+        <v>179</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>43</v>
@@ -3110,27 +3142,27 @@
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="J36" s="3">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>43</v>
@@ -3140,27 +3172,27 @@
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="J37" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>174</v>
+        <v>49</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>43</v>
@@ -3170,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="J38" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -3190,7 +3222,7 @@
         <v>188</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>38</v>
@@ -3206,7 +3238,7 @@
         <v>190</v>
       </c>
       <c r="J39" s="3">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40">
@@ -3220,7 +3252,7 @@
         <v>193</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>43</v>
@@ -3233,51 +3265,51 @@
         <v>194</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>195</v>
+        <v>63</v>
       </c>
       <c r="J40" s="3">
-        <v>45</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>196</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>60</v>
+        <v>197</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="J41" s="3">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>157</v>
+        <v>201</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>49</v>
@@ -3290,57 +3322,57 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>155</v>
+        <v>203</v>
       </c>
       <c r="J42" s="3">
-        <v>2</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>120</v>
+        <v>204</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>49</v>
+        <v>206</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>161</v>
+        <v>208</v>
       </c>
       <c r="J43" s="3">
-        <v>67</v>
+        <v>91</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>203</v>
+        <v>124</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>172</v>
+        <v>209</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>173</v>
+        <v>60</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>174</v>
+        <v>49</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>43</v>
@@ -3350,57 +3382,57 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="J44" s="3">
-        <v>3</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>120</v>
+        <v>212</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="E45" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="J45" s="3">
-        <v>58</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>157</v>
+        <v>217</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>49</v>
+        <v>179</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>43</v>
@@ -3410,103 +3442,103 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="J46" s="3">
-        <v>89</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>214</v>
+        <v>161</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>215</v>
+        <v>49</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J47" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>53</v>
+        <v>124</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>193</v>
+        <v>224</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>220</v>
+        <v>165</v>
       </c>
       <c r="J48" s="3">
-        <v>43</v>
+        <v>69</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>221</v>
+        <v>53</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="J49" s="3">
-        <v>71</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50">
@@ -3514,13 +3546,13 @@
         <v>53</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>38</v>
@@ -3530,54 +3562,54 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>63</v>
       </c>
       <c r="J50" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>157</v>
+        <v>227</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="J51" s="3">
-        <v>71</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>49</v>
@@ -3590,84 +3622,84 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="J52" s="3">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>120</v>
+        <v>239</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>185</v>
+        <v>244</v>
       </c>
       <c r="J53" s="3">
-        <v>3</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>238</v>
+        <v>124</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>193</v>
+        <v>246</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>49</v>
+        <v>179</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="J54" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>178</v>
+        <v>249</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>49</v>
@@ -3680,24 +3712,24 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>165</v>
+        <v>219</v>
       </c>
       <c r="J55" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>244</v>
+        <v>181</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>49</v>
@@ -3710,54 +3742,54 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>77</v>
+        <v>253</v>
       </c>
       <c r="J56" s="3">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>157</v>
+        <v>60</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="J57" s="3">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>157</v>
+        <v>227</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>49</v>
@@ -3770,27 +3802,27 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="J58" s="3">
-        <v>67</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>253</v>
+        <v>161</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>254</v>
+        <v>49</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>38</v>
@@ -3800,24 +3832,24 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>256</v>
+        <v>208</v>
       </c>
       <c r="J59" s="3">
-        <v>28</v>
+        <v>91</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>257</v>
+        <v>86</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>49</v>
@@ -3830,54 +3862,54 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="J60" s="3">
-        <v>45</v>
+        <v>69</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>168</v>
+        <v>265</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>77</v>
+        <v>235</v>
       </c>
       <c r="J61" s="3">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>152</v>
+        <v>267</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>262</v>
+        <v>168</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>49</v>
@@ -3890,27 +3922,27 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="J62" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>260</v>
+        <v>156</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>265</v>
+        <v>161</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>43</v>
@@ -3920,24 +3952,24 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>185</v>
+        <v>99</v>
       </c>
       <c r="J63" s="3">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>178</v>
+        <v>260</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>49</v>
@@ -3950,24 +3982,24 @@
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J64" s="3">
-        <v>1</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>120</v>
+        <v>273</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>49</v>
@@ -3980,10 +4012,10 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="J65" s="3">
         <v>32</v>
@@ -3994,10 +4026,10 @@
         <v>53</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>49</v>
@@ -4010,54 +4042,54 @@
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="J66" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>274</v>
+        <v>53</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>185</v>
+        <v>280</v>
       </c>
       <c r="J67" s="3">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>243</v>
+        <v>56</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>49</v>
@@ -4070,54 +4102,54 @@
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>77</v>
+        <v>283</v>
       </c>
       <c r="J68" s="3">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>243</v>
+        <v>284</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>157</v>
+        <v>60</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>63</v>
+        <v>219</v>
       </c>
       <c r="J69" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>53</v>
+        <v>239</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>157</v>
+        <v>201</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>49</v>
@@ -4130,86 +4162,86 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>283</v>
+        <v>81</v>
       </c>
       <c r="J70" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>284</v>
+        <v>124</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>227</v>
+        <v>60</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F71" s="3" t="s">
-        <v>286</v>
-      </c>
+      <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>77</v>
+        <v>219</v>
       </c>
       <c r="J71" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F72" s="3"/>
+      <c r="F72" s="3" t="s">
+        <v>293</v>
+      </c>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="J72" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>49</v>
@@ -4222,24 +4254,24 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J73" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>49</v>
@@ -4252,27 +4284,27 @@
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>63</v>
       </c>
       <c r="J74" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>172</v>
+        <v>300</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>214</v>
+        <v>161</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>215</v>
+        <v>49</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>38</v>
@@ -4282,27 +4314,27 @@
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="J75" s="3">
-        <v>89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>236</v>
+        <v>304</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>43</v>
@@ -4312,24 +4344,24 @@
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="J76" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>300</v>
+        <v>124</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>49</v>
@@ -4342,43 +4374,43 @@
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>303</v>
+        <v>159</v>
       </c>
       <c r="J77" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>149</v>
+        <v>308</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>304</v>
+        <v>171</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>303</v>
+        <v>173</v>
       </c>
       <c r="J78" s="3">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79">
@@ -4386,13 +4418,13 @@
         <v>53</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>38</v>
@@ -4402,27 +4434,27 @@
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="J79" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>43</v>
@@ -4432,27 +4464,27 @@
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J80" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>312</v>
+        <v>212</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>253</v>
+        <v>161</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>254</v>
+        <v>49</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>38</v>
@@ -4462,57 +4494,57 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>185</v>
+        <v>235</v>
       </c>
       <c r="J81" s="3">
-        <v>3</v>
+        <v>47</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>316</v>
+        <v>182</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>130</v>
+        <v>37</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>318</v>
+        <v>219</v>
       </c>
       <c r="J82" s="3">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>38</v>
@@ -4522,24 +4554,24 @@
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="J83" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>322</v>
+        <v>124</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>49</v>
@@ -4547,9 +4579,7 @@
       <c r="E84" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F84" s="3" t="s">
-        <v>324</v>
-      </c>
+      <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
@@ -4557,10 +4587,10 @@
         <v>325</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>77</v>
+        <v>208</v>
       </c>
       <c r="J84" s="3">
-        <v>1</v>
+        <v>91</v>
       </c>
     </row>
     <row r="85">
@@ -4571,15 +4601,17 @@
         <v>327</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>328</v>
+        <v>201</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F85" s="3"/>
+      <c r="F85" s="3" t="s">
+        <v>328</v>
+      </c>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
@@ -4587,10 +4619,10 @@
         <v>329</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="J85" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -4598,13 +4630,13 @@
         <v>330</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>168</v>
+        <v>331</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>157</v>
+        <v>332</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>43</v>
@@ -4614,30 +4646,30 @@
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>332</v>
+        <v>63</v>
       </c>
       <c r="J86" s="3">
-        <v>73</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>334</v>
+        <v>192</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
@@ -4647,10 +4679,10 @@
         <v>335</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="J87" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -4661,13 +4693,13 @@
         <v>337</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
@@ -4677,10 +4709,10 @@
         <v>338</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>185</v>
+        <v>113</v>
       </c>
       <c r="J88" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
@@ -4691,13 +4723,13 @@
         <v>340</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
@@ -4707,10 +4739,10 @@
         <v>341</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="J89" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
@@ -4721,10 +4753,10 @@
         <v>343</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>344</v>
+        <v>201</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>174</v>
+        <v>49</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>43</v>
@@ -4734,17 +4766,107 @@
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="J90" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="I90" s="3" t="s">
+      <c r="D91" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="J91" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="I93" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J90" s="3">
-        <v>0</v>
+      <c r="J93" s="3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J90"/>
+  <autoFilter ref="A1:J93"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4835,6 +4957,9 @@
     <hyperlink ref="H88" r:id="rId87"/>
     <hyperlink ref="H89" r:id="rId88"/>
     <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4842,7 +4967,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="48" customWidth="1"/>
+    <col min="1" max="1" width="50" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
@@ -4876,13 +5001,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -4890,37 +5015,37 @@
         <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>124</v>
+        <v>299</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>125</v>
+        <v>300</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>49</v>
+        <v>161</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>127</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>120</v>
+        <v>302</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>156</v>
+        <v>303</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -4928,18 +5053,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>158</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>334</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -4947,18 +5072,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>228</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>243</v>
+        <v>347</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>157</v>
+        <v>345</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -4966,97 +5091,17 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
     <hyperlink ref="G4" r:id="rId3"/>
     <hyperlink ref="G5" r:id="rId4"/>
     <hyperlink ref="G6" r:id="rId5"/>
-    <hyperlink ref="G7" r:id="rId6"/>
-    <hyperlink ref="G8" r:id="rId7"/>
-    <hyperlink ref="G9" r:id="rId8"/>
-    <hyperlink ref="G10" r:id="rId9"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5070,111 +5115,111 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B2" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B4" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B8" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="B11" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -5182,7 +5227,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5190,10 +5235,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5203,7 +5248,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5212,7 +5257,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2">
@@ -5220,12 +5265,12 @@
         <v>70</v>
       </c>
       <c r="B2" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B3" s="3">
         <v>4</v>
@@ -5233,15 +5278,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>48</v>
+        <v>260</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>168</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5249,7 +5294,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>172</v>
+        <v>303</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5257,23 +5302,23 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>178</v>
+        <v>35</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>247</v>
+        <v>108</v>
       </c>
       <c r="B8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5281,7 +5326,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5289,7 +5334,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5297,7 +5342,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5305,7 +5350,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5313,7 +5358,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>306</v>
+        <v>177</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5321,18 +5366,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>59</v>
+        <v>181</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>65</v>
+        <v>192</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5343,23 +5388,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2">
@@ -5367,13 +5412,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="C2" s="3">
-        <v>16.8</v>
+        <v>18.6</v>
       </c>
       <c r="D2" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -5381,13 +5426,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="C3" s="3">
-        <v>10.9</v>
+        <v>16.8</v>
       </c>
       <c r="D3" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -5395,13 +5440,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="C4" s="3">
-        <v>10.1</v>
+        <v>10.9</v>
       </c>
       <c r="D4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -5423,7 +5468,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C6" s="3">
         <v>6.0</v>
@@ -5437,7 +5482,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C7" s="3">
         <v>5.8</v>
@@ -5451,7 +5496,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C8" s="3">
         <v>5.3</v>
@@ -5465,7 +5510,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C9" s="3">
         <v>5.0</v>
@@ -5479,13 +5524,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>172</v>
+        <v>260</v>
       </c>
       <c r="C10" s="3">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -5493,10 +5538,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>178</v>
+        <v>303</v>
       </c>
       <c r="C11" s="3">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="D11" s="3">
         <v>3</v>
@@ -5507,13 +5552,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>168</v>
+        <v>125</v>
       </c>
       <c r="C12" s="3">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="D12" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -5521,13 +5566,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>247</v>
+        <v>177</v>
       </c>
       <c r="C13" s="3">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="D13" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -5535,13 +5580,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>121</v>
+        <v>181</v>
       </c>
       <c r="C14" s="3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -5549,13 +5594,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>59</v>
+        <v>192</v>
       </c>
       <c r="C15" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -5563,13 +5608,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>306</v>
+        <v>59</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
       </c>
       <c r="D16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5589,15 +5634,15 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -5614,7 +5659,7 @@
         <v>45</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4">
@@ -5622,10 +5667,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -5644,7 +5689,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2">
@@ -5652,23 +5697,23 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B3" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -5676,20 +5721,20 @@
         <v>37</v>
       </c>
       <c r="B5" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>254</v>
+        <v>116</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>112</v>
+        <v>206</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5697,7 +5742,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>215</v>
+        <v>242</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5724,10 +5769,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5739,10 +5784,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5759,31 +5804,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3">
@@ -5791,31 +5836,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>185</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4">
@@ -5823,31 +5868,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>163</v>
+        <v>60</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>77</v>
+        <v>389</v>
       </c>
     </row>
     <row r="5">
@@ -5855,31 +5900,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>383</v>
+        <v>300</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>386</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6">
@@ -5887,31 +5932,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>157</v>
+        <v>201</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7">
@@ -5919,31 +5964,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="F7" s="3">
         <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8">
@@ -5951,31 +5996,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>396</v>
+        <v>168</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="F8" s="3">
         <v>100</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9">
@@ -5983,31 +6028,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>330</v>
+        <v>95</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>168</v>
+        <v>90</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="F9" s="3">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>331</v>
+        <v>98</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>133</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
@@ -6015,31 +6060,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>91</v>
+        <v>405</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>86</v>
+        <v>406</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>87</v>
+        <v>407</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F10" s="3">
         <v>92</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>94</v>
+        <v>409</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>95</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11">
@@ -6047,31 +6092,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>401</v>
+        <v>42</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>402</v>
+        <v>35</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>403</v>
+        <v>36</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F11" s="3">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>405</v>
+        <v>45</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>406</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -6079,31 +6124,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>330</v>
+        <v>412</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>370</v>
+        <v>413</v>
       </c>
       <c r="F12" s="3">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>409</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13">
@@ -6111,7 +6156,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>42</v>
+        <v>416</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>35</v>
@@ -6120,22 +6165,22 @@
         <v>36</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F13" s="3">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>45</v>
+        <v>418</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>46</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14">
@@ -6143,31 +6188,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>378</v>
+        <v>420</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F14" s="3">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>77</v>
+        <v>423</v>
       </c>
     </row>
     <row r="15">
@@ -6175,31 +6220,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>227</v>
+        <v>197</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>416</v>
+        <v>377</v>
       </c>
       <c r="F15" s="3">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>165</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -6207,31 +6252,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>298</v>
+        <v>429</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="F16" s="3">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>77</v>
+        <v>432</v>
       </c>
     </row>
     <row r="17">
@@ -6239,31 +6284,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>35</v>
+        <v>233</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>36</v>
+        <v>161</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>370</v>
+        <v>413</v>
       </c>
       <c r="F17" s="3">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>165</v>
+        <v>436</v>
       </c>
     </row>
     <row r="18">
@@ -6271,31 +6316,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="F18" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>429</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
@@ -6303,31 +6348,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>370</v>
+        <v>443</v>
       </c>
       <c r="F19" s="3">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20">
@@ -6335,31 +6380,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>316</v>
+        <v>161</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="F20" s="3">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>119</v>
+        <v>450</v>
       </c>
     </row>
     <row r="21">
@@ -6367,31 +6412,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>438</v>
+        <v>184</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="F21" s="3">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>441</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
